--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6DD825-C787-42F6-B89E-E6C0C591DEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D281EC90-03B6-4BAC-B540-8373AA234E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="612">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -2166,6 +2166,288 @@
   <si>
     <t>絕對不能被「彷徨者 」抓住</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageRussian</t>
+  </si>
+  <si>
+    <t>speakerNameRussian</t>
+  </si>
+  <si>
+    <t>messageSizeRussian</t>
+  </si>
+  <si>
+    <t>Где… где я?</t>
+  </si>
+  <si>
+    <t>Вы</t>
+  </si>
+  <si>
+    <t>Похоже, ты очнулся.</t>
+  </si>
+  <si>
+    <t>Меня зовут Канамэ.
+Я проводник по «Мумэю».</t>
+  </si>
+  <si>
+    <t>Канамэ</t>
+  </si>
+  <si>
+    <t>Мумэй?</t>
+  </si>
+  <si>
+    <t>Это огромный лабиринт, что находится здесь, в Вечном мире.</t>
+  </si>
+  <si>
+    <t>Ты умер в мире живых, совершив «грех».
+Все, кто согрешил, заточены здесь, в Мумэе.</t>
+  </si>
+  <si>
+    <t>Иными словами, ты — один из них.</t>
+  </si>
+  <si>
+    <t>Грех?</t>
+  </si>
+  <si>
+    <t>Да. Очень-очень тяжкий грех.</t>
+  </si>
+  <si>
+    <t>Кстати, ты помнишь своё имя?</t>
+  </si>
+  <si>
+    <t>Эм… меня зовут…</t>
+  </si>
+  <si>
+    <t>Что?.. Не помню……</t>
+  </si>
+  <si>
+    <t>Неудивительно, что не помнишь.</t>
+  </si>
+  <si>
+    <t>Ведь твоё имя уничтожили ещё до того, как ты попал в этот лабиринт.</t>
+  </si>
+  <si>
+    <t>Моё имя… уничтожили?..</t>
+  </si>
+  <si>
+    <t>Что это значит?</t>
+  </si>
+  <si>
+    <t>Тот, чьё имя уничтожено в Вечном мире,
+не может вспомнить его сам.</t>
+  </si>
+  <si>
+    <t>Что……</t>
+  </si>
+  <si>
+    <t>А тот, кто не может вспомнить своё имя…</t>
+  </si>
+  <si>
+    <t>…обречён вечно скитаться по этому лабиринту,
+терпя все мыслимые муки.</t>
+  </si>
+  <si>
+    <t>Рано или поздно и тебя ждёт то же самое.</t>
+  </si>
+  <si>
+    <t>Нет… это слишком жестоко…</t>
+  </si>
+  <si>
+    <t>Почему…</t>
+  </si>
+  <si>
+    <t>Потому что грешникам имена ни к чему.</t>
+  </si>
+  <si>
+    <t>Но не волнуйся.</t>
+  </si>
+  <si>
+    <t>Если вспомнишь грех, совершённый в мире живых, и выберешься из этого лабиринта,
+я скажу тебе твоё имя.</t>
+  </si>
+  <si>
+    <t>Тогда тебе не придётся ни страдать,
+ни скитаться.</t>
+  </si>
+  <si>
+    <t>…Хочешь выбраться отсюда?</t>
+  </si>
+  <si>
+    <t>……Хочу выбраться.</t>
+  </si>
+  <si>
+    <t>Но как отсюда выбраться?</t>
+  </si>
+  <si>
+    <t>…Есть один способ.</t>
+  </si>
+  <si>
+    <t>Принять моё испытание и выдержать его.</t>
+  </si>
+  <si>
+    <t>Тогда ты сможешь выбраться.</t>
+  </si>
+  <si>
+    <t>…Примешь моё испытание?</t>
+  </si>
+  <si>
+    <t>……Приму.</t>
+  </si>
+  <si>
+    <t>…Хорошо.
+Тогда я объясню, в чём состоит испытание.</t>
+  </si>
+  <si>
+    <t>Чтобы пройти испытание,
+нужно выполнить два условия.</t>
+  </si>
+  <si>
+    <t>Первое: выбраться из этого лабиринта.
+Второе: вспомнить грех, совершённый тобой в мире живых.</t>
+  </si>
+  <si>
+    <t>Я расскажу, как выбраться из этого лабиринта.</t>
+  </si>
+  <si>
+    <t>Чтобы выбраться, нужно отыскать «Документы» и «Загадочные предметы»,
+спрятанные по всему лабиринту.</t>
+  </si>
+  <si>
+    <t>Сначала добудь Документ.
+Для начала открой ящик прямо перед тобой.</t>
+  </si>
+  <si>
+    <t>Теперь прочти Документ, который ты только что взял.</t>
+  </si>
+  <si>
+    <t>Теперь добудь Загадочный предмет.</t>
+  </si>
+  <si>
+    <t>Открой два ящика прямо перед тобой.</t>
+  </si>
+  <si>
+    <t>Теперь осмотри Загадочные предметы, которые ты только что взял.</t>
+  </si>
+  <si>
+    <t>И наконец, коснись «Синей сферы Правосудия» в глубине.</t>
+  </si>
+  <si>
+    <t>Выбери Загадочный предмет, тесно связанный
+с содержанием Документа.</t>
+  </si>
+  <si>
+    <t>На этом объяснение испытания окончено.
+Есть вопросы?</t>
+  </si>
+  <si>
+    <t>А? Ты не расскажешь, какой грех я совершил?</t>
+  </si>
+  <si>
+    <t>Не расскажу.</t>
+  </si>
+  <si>
+    <t>Никаких «что».</t>
+  </si>
+  <si>
+    <t>Если ты по-настоящему раскаиваешься,
+то сразу же вспомнишь свой грех.</t>
+  </si>
+  <si>
+    <t>Поэтому объяснение на этом окончено.</t>
+  </si>
+  <si>
+    <t>И ещё: без имени неудобно,
+поэтому пока я буду звать тебя «Иф».</t>
+  </si>
+  <si>
+    <t>Ты ведь не против?</t>
+  </si>
+  <si>
+    <t>Э… д-да……</t>
+  </si>
+  <si>
+    <t>Напоследок — одно важное предупреждение об этом лабиринте.</t>
+  </si>
+  <si>
+    <t>Предупреждение?</t>
+  </si>
+  <si>
+    <t>Ни в коем случае не попадайся «Скитальцам».</t>
+  </si>
+  <si>
+    <t>Скитальцам?</t>
+  </si>
+  <si>
+    <t>Так зовут чудовищ, что таятся в Мумэе.</t>
+  </si>
+  <si>
+    <t>Иф, главное — не дай этим чудовищам себя поймать.</t>
+  </si>
+  <si>
+    <t>Понял?</t>
+  </si>
+  <si>
+    <t>……Д-да……</t>
+  </si>
+  <si>
+    <t>Что ж, начнём испытание.
+Проходи в коридор позади тебя.</t>
+  </si>
+  <si>
+    <t>Иф, я буду молиться, чтобы ты прошёл испытание.</t>
+  </si>
+  <si>
+    <t>…Наконец-то… я выберусь из этого лабиринта…</t>
+  </si>
+  <si>
+    <t>Что… что это……</t>
+  </si>
+  <si>
+    <t>Почему лабиринт всё ещё не кончился?!</t>
+  </si>
+  <si>
+    <t>А разве не очевидно?</t>
+  </si>
+  <si>
+    <t>Потому что ты ещё не выбрался из лабиринта.</t>
+  </si>
+  <si>
+    <t>…Как это — не выбрался?</t>
+  </si>
+  <si>
+    <t>Я же собрал и Документы,
+и Загадочные предметы!</t>
+  </si>
+  <si>
+    <t>Неужели ты думал, что на этом всё?</t>
+  </si>
+  <si>
+    <t>Документы и Загадочные предметы
+есть и в других зонах.</t>
+  </si>
+  <si>
+    <t>Не может быть…</t>
+  </si>
+  <si>
+    <t>К тому же, Иф, ты ещё не вспомнил свой грех, верно?</t>
+  </si>
+  <si>
+    <t>…!</t>
+  </si>
+  <si>
+    <t>Поэтому испытание ещё не окончено.</t>
+  </si>
+  <si>
+    <t>Нет……</t>
+  </si>
+  <si>
+    <t>Настоящий ужас Мумэя только начинается, Иф.</t>
+  </si>
+  <si>
+    <t>Знаю, тебе нелегко,</t>
+  </si>
+  <si>
+    <t>но давай и дальше стараться, Иф.</t>
   </si>
 </sst>
 </file>
@@ -2534,7 +2816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA102"/>
+  <dimension ref="A1:AD102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -2554,16 +2836,19 @@
     <col min="17" max="17" width="47.125" customWidth="1"/>
     <col min="18" max="18" width="24.875" customWidth="1"/>
     <col min="19" max="19" width="29.375" customWidth="1"/>
-    <col min="20" max="20" width="27.75" customWidth="1"/>
-    <col min="21" max="21" width="22.5" customWidth="1"/>
-    <col min="22" max="22" width="13.625" customWidth="1"/>
-    <col min="24" max="24" width="17.125" customWidth="1"/>
-    <col min="25" max="25" width="28.125" customWidth="1"/>
-    <col min="26" max="26" width="13.125" customWidth="1"/>
-    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="20" max="20" width="104.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.75" customWidth="1"/>
+    <col min="24" max="24" width="22.5" customWidth="1"/>
+    <col min="25" max="25" width="13.625" customWidth="1"/>
+    <col min="27" max="27" width="17.125" customWidth="1"/>
+    <col min="28" max="28" width="28.125" customWidth="1"/>
+    <col min="29" max="29" width="13.125" customWidth="1"/>
+    <col min="30" max="30" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2622,31 +2907,40 @@
         <v>521</v>
       </c>
       <c r="T1" t="s">
+        <v>524</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="V1" t="s">
+        <v>526</v>
+      </c>
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="U1" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:30">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2672,12 +2966,6 @@
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
       <c r="V2">
         <v>0</v>
       </c>
@@ -2696,8 +2984,17 @@
       <c r="AA2">
         <v>0</v>
       </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:30">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2755,14 +3052,14 @@
       <c r="S3">
         <v>22</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
+      <c r="T3" t="s">
+        <v>527</v>
+      </c>
+      <c r="U3" t="s">
+        <v>528</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -2779,8 +3076,17 @@
       <c r="AA3">
         <v>0</v>
       </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:30">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2838,32 +3144,41 @@
       <c r="S4">
         <v>22</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="s">
+        <v>529</v>
+      </c>
+      <c r="U4" t="s">
+        <v>192</v>
+      </c>
+      <c r="V4">
+        <v>22</v>
+      </c>
+      <c r="W4">
         <v>1</v>
       </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
         <v>3</v>
       </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
       <c r="AA4">
         <v>0</v>
       </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" ht="37.5">
+    <row r="5" spans="1:30" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2921,14 +3236,14 @@
       <c r="S5">
         <v>22</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
+      <c r="T5" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="U5" t="s">
+        <v>531</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -2945,8 +3260,17 @@
       <c r="AA5">
         <v>0</v>
       </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:30">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3004,14 +3328,14 @@
       <c r="S6">
         <v>22</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
+      <c r="T6" t="s">
+        <v>532</v>
+      </c>
+      <c r="U6" t="s">
+        <v>528</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -3028,8 +3352,17 @@
       <c r="AA6">
         <v>0</v>
       </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:30">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3087,14 +3420,14 @@
       <c r="S7">
         <v>22</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
+      <c r="T7" t="s">
+        <v>533</v>
+      </c>
+      <c r="U7" t="s">
+        <v>531</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -3111,8 +3444,17 @@
       <c r="AA7">
         <v>0</v>
       </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" ht="75">
+    <row r="8" spans="1:30" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3170,14 +3512,14 @@
       <c r="S8">
         <v>22</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
+      <c r="T8" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="U8" t="s">
+        <v>531</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -3194,8 +3536,17 @@
       <c r="AA8">
         <v>0</v>
       </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:30">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3253,14 +3604,14 @@
       <c r="S9">
         <v>22</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
+      <c r="T9" t="s">
+        <v>535</v>
+      </c>
+      <c r="U9" t="s">
+        <v>531</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -3277,8 +3628,17 @@
       <c r="AA9">
         <v>0</v>
       </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:30">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3336,14 +3696,14 @@
       <c r="S10">
         <v>22</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
+      <c r="T10" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="U10" t="s">
+        <v>528</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -3360,8 +3720,17 @@
       <c r="AA10">
         <v>0</v>
       </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:30">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3419,14 +3788,14 @@
       <c r="S11">
         <v>22</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
+      <c r="T11" t="s">
+        <v>537</v>
+      </c>
+      <c r="U11" t="s">
+        <v>531</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -3443,8 +3812,17 @@
       <c r="AA11">
         <v>0</v>
       </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:30">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3502,14 +3880,14 @@
       <c r="S12">
         <v>22</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
+      <c r="T12" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="U12" t="s">
+        <v>531</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -3526,8 +3904,17 @@
       <c r="AA12">
         <v>0</v>
       </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:30">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3585,21 +3972,21 @@
       <c r="S13">
         <v>22</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
+      <c r="T13" t="s">
+        <v>539</v>
+      </c>
+      <c r="U13" t="s">
+        <v>528</v>
+      </c>
+      <c r="V13">
+        <v>22</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
         <v>1</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
       <c r="Y13">
         <v>0</v>
       </c>
@@ -3609,8 +3996,17 @@
       <c r="AA13">
         <v>0</v>
       </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:30">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3668,14 +4064,14 @@
       <c r="S14">
         <v>22</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
+      <c r="T14" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="U14" t="s">
+        <v>528</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W14">
         <v>0</v>
@@ -3692,8 +4088,17 @@
       <c r="AA14">
         <v>0</v>
       </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:30">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3751,14 +4156,14 @@
       <c r="S15">
         <v>22</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
+      <c r="T15" t="s">
+        <v>541</v>
+      </c>
+      <c r="U15" t="s">
+        <v>531</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -3775,8 +4180,17 @@
       <c r="AA15">
         <v>0</v>
       </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:27" ht="37.5">
+    <row r="16" spans="1:30" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3834,14 +4248,14 @@
       <c r="S16">
         <v>22</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
+      <c r="T16" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="U16" t="s">
+        <v>531</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W16">
         <v>0</v>
@@ -3858,8 +4272,17 @@
       <c r="AA16">
         <v>0</v>
       </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:30">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3917,14 +4340,14 @@
       <c r="S17">
         <v>22</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
+      <c r="T17" t="s">
+        <v>543</v>
+      </c>
+      <c r="U17" t="s">
+        <v>528</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W17">
         <v>0</v>
@@ -3941,8 +4364,17 @@
       <c r="AA17">
         <v>0</v>
       </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:30">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4000,14 +4432,14 @@
       <c r="S18">
         <v>22</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
+      <c r="T18" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="U18" t="s">
+        <v>528</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -4024,8 +4456,17 @@
       <c r="AA18">
         <v>0</v>
       </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:27" ht="56.25">
+    <row r="19" spans="1:30" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4083,14 +4524,14 @@
       <c r="S19">
         <v>22</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
+      <c r="T19" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="U19" t="s">
+        <v>531</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -4107,8 +4548,17 @@
       <c r="AA19">
         <v>0</v>
       </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:30">
       <c r="A20">
         <v>18</v>
       </c>
@@ -4166,14 +4616,14 @@
       <c r="S20">
         <v>22</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
+      <c r="T20" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="U20" t="s">
+        <v>528</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -4190,8 +4640,17 @@
       <c r="AA20">
         <v>0</v>
       </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:30" ht="37.5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -4246,21 +4705,21 @@
       <c r="S21">
         <v>22</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
+      <c r="T21" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="U21" t="s">
+        <v>531</v>
+      </c>
+      <c r="V21">
+        <v>22</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
         <v>1</v>
       </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
       <c r="Y21">
         <v>0</v>
       </c>
@@ -4270,8 +4729,17 @@
       <c r="AA21">
         <v>0</v>
       </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:27" ht="37.5">
+    <row r="22" spans="1:30" ht="56.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -4329,14 +4797,14 @@
       <c r="S22">
         <v>22</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
+      <c r="T22" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="U22" t="s">
+        <v>531</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -4353,8 +4821,17 @@
       <c r="AA22">
         <v>0</v>
       </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:27" ht="37.5">
+    <row r="23" spans="1:30" ht="37.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -4412,14 +4889,14 @@
       <c r="S23">
         <v>22</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
+      <c r="T23" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="U23" t="s">
+        <v>531</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -4436,8 +4913,17 @@
       <c r="AA23">
         <v>0</v>
       </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:30">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4495,14 +4981,14 @@
       <c r="S24">
         <v>22</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
+      <c r="T24" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="U24" t="s">
+        <v>528</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -4519,8 +5005,17 @@
       <c r="AA24">
         <v>0</v>
       </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:30">
       <c r="A25">
         <v>23</v>
       </c>
@@ -4578,14 +5073,14 @@
       <c r="S25">
         <v>22</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
+      <c r="T25" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="U25" t="s">
+        <v>528</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -4602,8 +5097,17 @@
       <c r="AA25">
         <v>0</v>
       </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:30" ht="37.5">
       <c r="A26">
         <v>24</v>
       </c>
@@ -4661,14 +5165,14 @@
       <c r="S26">
         <v>22</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
+      <c r="T26" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="U26" t="s">
+        <v>531</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -4685,8 +5189,17 @@
       <c r="AA26">
         <v>0</v>
       </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:30">
       <c r="A27">
         <v>25</v>
       </c>
@@ -4744,14 +5257,14 @@
       <c r="S27">
         <v>22</v>
       </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
+      <c r="T27" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="U27" t="s">
+        <v>531</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -4768,8 +5281,17 @@
       <c r="AA27">
         <v>0</v>
       </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:27" ht="56.25">
+    <row r="28" spans="1:30" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4827,14 +5349,14 @@
       <c r="S28">
         <v>22</v>
       </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
+      <c r="T28" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="U28" t="s">
+        <v>531</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W28">
         <v>0</v>
@@ -4851,8 +5373,17 @@
       <c r="AA28">
         <v>0</v>
       </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:27" ht="37.5">
+    <row r="29" spans="1:30" ht="56.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -4910,32 +5441,41 @@
       <c r="S29">
         <v>22</v>
       </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
+      <c r="T29" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="U29" t="s">
+        <v>531</v>
       </c>
       <c r="V29">
+        <v>22</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
         <v>1</v>
       </c>
-      <c r="W29">
+      <c r="Z29">
         <v>1</v>
       </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
       <c r="AA29">
         <v>0</v>
       </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:30">
       <c r="A30">
         <v>28</v>
       </c>
@@ -4993,14 +5533,14 @@
       <c r="S30">
         <v>22</v>
       </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
+      <c r="T30" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="U30" t="s">
+        <v>531</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W30">
         <v>0</v>
@@ -5017,8 +5557,17 @@
       <c r="AA30">
         <v>0</v>
       </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:30">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5076,14 +5625,14 @@
       <c r="S31">
         <v>22</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
+      <c r="T31" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="U31" t="s">
+        <v>528</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5100,8 +5649,17 @@
       <c r="AA31">
         <v>0</v>
       </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:30">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5159,14 +5717,14 @@
       <c r="S32">
         <v>22</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
+      <c r="T32" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="U32" t="s">
+        <v>528</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W32">
         <v>0</v>
@@ -5183,8 +5741,17 @@
       <c r="AA32">
         <v>0</v>
       </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:30">
       <c r="A33">
         <v>31</v>
       </c>
@@ -5242,14 +5809,14 @@
       <c r="S33">
         <v>22</v>
       </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
+      <c r="T33" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="U33" t="s">
+        <v>531</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W33">
         <v>0</v>
@@ -5266,8 +5833,17 @@
       <c r="AA33">
         <v>0</v>
       </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:27" ht="37.5">
+    <row r="34" spans="1:30" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -5325,14 +5901,14 @@
       <c r="S34">
         <v>22</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
+      <c r="T34" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="U34" t="s">
+        <v>531</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W34">
         <v>0</v>
@@ -5349,8 +5925,17 @@
       <c r="AA34">
         <v>0</v>
       </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:30">
       <c r="A35">
         <v>33</v>
       </c>
@@ -5408,32 +5993,41 @@
       <c r="S35">
         <v>22</v>
       </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
+      <c r="T35" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="U35" t="s">
+        <v>531</v>
       </c>
       <c r="V35">
+        <v>22</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
         <v>1</v>
       </c>
-      <c r="W35">
+      <c r="Z35">
         <v>1</v>
       </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
       <c r="AA35">
         <v>0</v>
       </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:30">
       <c r="A36">
         <v>34</v>
       </c>
@@ -5491,14 +6085,14 @@
       <c r="S36">
         <v>22</v>
       </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
+      <c r="T36" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="U36" t="s">
+        <v>531</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -5515,8 +6109,17 @@
       <c r="AA36">
         <v>0</v>
       </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:30">
       <c r="A37">
         <v>35</v>
       </c>
@@ -5574,14 +6177,14 @@
       <c r="S37">
         <v>22</v>
       </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
+      <c r="T37" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="U37" t="s">
+        <v>528</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -5598,8 +6201,17 @@
       <c r="AA37">
         <v>0</v>
       </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:27" ht="37.5">
+    <row r="38" spans="1:30" ht="56.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -5657,32 +6269,41 @@
       <c r="S38">
         <v>22</v>
       </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
+      <c r="T38" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="U38" t="s">
+        <v>531</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W38">
         <v>0</v>
       </c>
       <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
         <v>1</v>
       </c>
-      <c r="Y38">
+      <c r="AB38">
         <v>9</v>
       </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
-      <c r="AA38">
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:30">
       <c r="A39">
         <v>37</v>
       </c>
@@ -5708,12 +6329,6 @@
       <c r="S39">
         <v>0</v>
       </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39">
-        <v>0</v>
-      </c>
       <c r="V39">
         <v>0</v>
       </c>
@@ -5732,8 +6347,17 @@
       <c r="AA39">
         <v>0</v>
       </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:27" ht="37.5">
+    <row r="40" spans="1:30" ht="56.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -5791,14 +6415,14 @@
       <c r="S40">
         <v>22</v>
       </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
+      <c r="T40" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="U40" t="s">
+        <v>531</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W40">
         <v>0</v>
@@ -5815,8 +6439,17 @@
       <c r="AA40">
         <v>0</v>
       </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:27" ht="85.5" customHeight="1">
+    <row r="41" spans="1:30" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -5874,14 +6507,14 @@
       <c r="S41">
         <v>22</v>
       </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
+      <c r="T41" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="U41" t="s">
+        <v>531</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -5898,8 +6531,17 @@
       <c r="AA41">
         <v>0</v>
       </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:27" ht="51.75" customHeight="1">
+    <row r="42" spans="1:30" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -5957,14 +6599,14 @@
       <c r="S42">
         <v>22</v>
       </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
+      <c r="T42" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="U42" t="s">
+        <v>531</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -5981,8 +6623,17 @@
       <c r="AA42">
         <v>0</v>
       </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:27" ht="56.25">
+    <row r="43" spans="1:30" ht="93.75">
       <c r="A43">
         <v>41</v>
       </c>
@@ -6040,14 +6691,14 @@
       <c r="S43">
         <v>22</v>
       </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
+      <c r="T43" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="U43" t="s">
+        <v>531</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W43">
         <v>0</v>
@@ -6064,8 +6715,17 @@
       <c r="AA43">
         <v>0</v>
       </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:27" ht="37.5">
+    <row r="44" spans="1:30" ht="56.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -6123,32 +6783,41 @@
       <c r="S44">
         <v>22</v>
       </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
+      <c r="T44" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="U44" t="s">
+        <v>531</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W44">
         <v>0</v>
       </c>
       <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
         <v>2</v>
       </c>
-      <c r="Y44">
+      <c r="AB44">
         <v>10</v>
       </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="56.25">
+    <row r="45" spans="1:30" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -6206,32 +6875,41 @@
       <c r="S45">
         <v>22</v>
       </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
+      <c r="T45" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="U45" t="s">
+        <v>531</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W45">
         <v>0</v>
       </c>
       <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
         <v>2</v>
       </c>
-      <c r="Y45">
+      <c r="AB45">
         <v>11</v>
       </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45">
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:30" ht="37.5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -6289,14 +6967,14 @@
       <c r="S46">
         <v>22</v>
       </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
+      <c r="T46" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="U46" t="s">
+        <v>531</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -6313,8 +6991,17 @@
       <c r="AA46">
         <v>0</v>
       </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:30" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -6372,32 +7059,41 @@
       <c r="S47">
         <v>22</v>
       </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
+      <c r="T47" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="U47" t="s">
+        <v>531</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W47">
         <v>0</v>
       </c>
       <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
         <v>3</v>
       </c>
-      <c r="Y47">
+      <c r="AB47">
         <v>12</v>
       </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-      <c r="AA47">
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:30" ht="56.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -6455,32 +7151,41 @@
       <c r="S48">
         <v>22</v>
       </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
+      <c r="T48" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="U48" t="s">
+        <v>531</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W48">
         <v>0</v>
       </c>
       <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
         <v>2</v>
       </c>
-      <c r="Y48">
+      <c r="AB48">
         <v>13</v>
       </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="37.5">
+    <row r="49" spans="1:30" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -6538,14 +7243,14 @@
       <c r="S49">
         <v>22</v>
       </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
+      <c r="T49" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="U49" t="s">
+        <v>531</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W49">
         <v>0</v>
@@ -6562,8 +7267,17 @@
       <c r="AA49">
         <v>0</v>
       </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:27" ht="56.25">
+    <row r="50" spans="1:30" ht="56.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -6621,32 +7335,41 @@
       <c r="S50">
         <v>22</v>
       </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
+      <c r="T50" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="U50" t="s">
+        <v>531</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W50">
         <v>0</v>
       </c>
       <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
         <v>2</v>
       </c>
-      <c r="Y50">
+      <c r="AB50">
         <v>14</v>
       </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="37.5">
+    <row r="51" spans="1:30" ht="56.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -6704,14 +7427,14 @@
       <c r="S51">
         <v>22</v>
       </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
+      <c r="T51" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="U51" t="s">
+        <v>531</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W51">
         <v>0</v>
@@ -6728,8 +7451,17 @@
       <c r="AA51">
         <v>0</v>
       </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:27" ht="37.5">
+    <row r="52" spans="1:30" ht="37.5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -6787,14 +7519,14 @@
       <c r="S52">
         <v>22</v>
       </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
+      <c r="T52" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="U52" t="s">
+        <v>528</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -6811,8 +7543,17 @@
       <c r="AA52">
         <v>0</v>
       </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:30">
       <c r="A53">
         <v>51</v>
       </c>
@@ -6870,14 +7611,14 @@
       <c r="S53">
         <v>22</v>
       </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
+      <c r="T53" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="U53" t="s">
+        <v>531</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -6894,8 +7635,17 @@
       <c r="AA53">
         <v>0</v>
       </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:30">
       <c r="A54">
         <v>52</v>
       </c>
@@ -6953,14 +7703,14 @@
       <c r="S54">
         <v>22</v>
       </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
+      <c r="T54" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="U54" t="s">
+        <v>528</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -6977,8 +7727,17 @@
       <c r="AA54">
         <v>0</v>
       </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:30">
       <c r="A55">
         <v>53</v>
       </c>
@@ -7036,14 +7795,14 @@
       <c r="S55">
         <v>22</v>
       </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-      <c r="U55">
-        <v>0</v>
+      <c r="T55" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="U55" t="s">
+        <v>531</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W55">
         <v>0</v>
@@ -7060,8 +7819,17 @@
       <c r="AA55">
         <v>0</v>
       </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:27" ht="56.25">
+    <row r="56" spans="1:30" ht="75">
       <c r="A56">
         <v>54</v>
       </c>
@@ -7119,14 +7887,14 @@
       <c r="S56">
         <v>22</v>
       </c>
-      <c r="T56">
-        <v>0</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
+      <c r="T56" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="U56" t="s">
+        <v>531</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W56">
         <v>0</v>
@@ -7143,8 +7911,17 @@
       <c r="AA56">
         <v>0</v>
       </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:27">
+    <row r="57" spans="1:30" ht="37.5">
       <c r="A57">
         <v>55</v>
       </c>
@@ -7202,14 +7979,14 @@
       <c r="S57">
         <v>22</v>
       </c>
-      <c r="T57">
-        <v>0</v>
-      </c>
-      <c r="U57">
-        <v>0</v>
+      <c r="T57" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="U57" t="s">
+        <v>531</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W57">
         <v>0</v>
@@ -7226,8 +8003,17 @@
       <c r="AA57">
         <v>0</v>
       </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:27" ht="37.5">
+    <row r="58" spans="1:30" ht="56.25">
       <c r="A58">
         <v>56</v>
       </c>
@@ -7285,14 +8071,14 @@
       <c r="S58">
         <v>22</v>
       </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
+      <c r="T58" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="U58" t="s">
+        <v>531</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W58">
         <v>0</v>
@@ -7309,8 +8095,17 @@
       <c r="AA58">
         <v>0</v>
       </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:30">
       <c r="A59">
         <v>57</v>
       </c>
@@ -7368,14 +8163,14 @@
       <c r="S59">
         <v>22</v>
       </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59">
-        <v>0</v>
+      <c r="T59" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="U59" t="s">
+        <v>531</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -7392,8 +8187,17 @@
       <c r="AA59">
         <v>0</v>
       </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:30">
       <c r="A60">
         <v>58</v>
       </c>
@@ -7451,14 +8255,14 @@
       <c r="S60">
         <v>22</v>
       </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
+      <c r="T60" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="U60" t="s">
+        <v>528</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -7475,8 +8279,17 @@
       <c r="AA60">
         <v>0</v>
       </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="1:27" ht="37.5">
+    <row r="61" spans="1:30" ht="56.25">
       <c r="A61">
         <v>59</v>
       </c>
@@ -7534,14 +8347,14 @@
       <c r="S61">
         <v>22</v>
       </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
+      <c r="T61" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="U61" t="s">
+        <v>531</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W61">
         <v>0</v>
@@ -7558,8 +8371,17 @@
       <c r="AA61">
         <v>0</v>
       </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="1:27">
+    <row r="62" spans="1:30">
       <c r="A62">
         <v>60</v>
       </c>
@@ -7617,21 +8439,21 @@
       <c r="S62">
         <v>22</v>
       </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62">
+      <c r="T62" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="U62" t="s">
+        <v>528</v>
+      </c>
+      <c r="V62">
+        <v>22</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
         <v>1</v>
       </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
       <c r="Y62">
         <v>0</v>
       </c>
@@ -7641,8 +8463,17 @@
       <c r="AA62">
         <v>0</v>
       </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="1:27">
+    <row r="63" spans="1:30" ht="37.5">
       <c r="A63">
         <v>61</v>
       </c>
@@ -7700,14 +8531,14 @@
       <c r="S63">
         <v>22</v>
       </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
+      <c r="T63" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="U63" t="s">
+        <v>531</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W63">
         <v>0</v>
@@ -7724,8 +8555,17 @@
       <c r="AA63">
         <v>0</v>
       </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="1:27">
+    <row r="64" spans="1:30">
       <c r="A64">
         <v>62</v>
       </c>
@@ -7783,14 +8623,14 @@
       <c r="S64">
         <v>22</v>
       </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
+      <c r="T64" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="U64" t="s">
+        <v>528</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W64">
         <v>0</v>
@@ -7807,8 +8647,17 @@
       <c r="AA64">
         <v>0</v>
       </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="1:27">
+    <row r="65" spans="1:30" ht="37.5">
       <c r="A65">
         <v>63</v>
       </c>
@@ -7866,14 +8715,14 @@
       <c r="S65">
         <v>22</v>
       </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
+      <c r="T65" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="U65" t="s">
+        <v>531</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -7890,8 +8739,17 @@
       <c r="AA65">
         <v>0</v>
       </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:27" ht="37.5">
+    <row r="66" spans="1:30" ht="37.5">
       <c r="A66">
         <v>64</v>
       </c>
@@ -7949,14 +8807,14 @@
       <c r="S66">
         <v>22</v>
       </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
+      <c r="T66" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="U66" t="s">
+        <v>531</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -7973,8 +8831,17 @@
       <c r="AA66">
         <v>0</v>
       </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="1:27">
+    <row r="67" spans="1:30">
       <c r="A67">
         <v>65</v>
       </c>
@@ -8032,14 +8899,14 @@
       <c r="S67">
         <v>22</v>
       </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
+      <c r="T67" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="U67" t="s">
+        <v>531</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -8056,8 +8923,17 @@
       <c r="AA67">
         <v>0</v>
       </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
     </row>
-    <row r="68" spans="1:27">
+    <row r="68" spans="1:30">
       <c r="A68">
         <v>66</v>
       </c>
@@ -8115,14 +8991,14 @@
       <c r="S68">
         <v>22</v>
       </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
+      <c r="T68" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="U68" t="s">
+        <v>528</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W68">
         <v>0</v>
@@ -8139,8 +9015,17 @@
       <c r="AA68">
         <v>0</v>
       </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="1:27" ht="37.5">
+    <row r="69" spans="1:30" ht="56.25">
       <c r="A69">
         <v>67</v>
       </c>
@@ -8198,14 +9083,14 @@
       <c r="S69">
         <v>22</v>
       </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
+      <c r="T69" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="U69" t="s">
+        <v>531</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -8222,8 +9107,17 @@
       <c r="AA69">
         <v>0</v>
       </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="1:27" ht="37.5">
+    <row r="70" spans="1:30" ht="37.5">
       <c r="A70">
         <v>68</v>
       </c>
@@ -8281,14 +9175,14 @@
       <c r="S70">
         <v>22</v>
       </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
+      <c r="T70" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="U70" t="s">
+        <v>531</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -8300,13 +9194,22 @@
         <v>0</v>
       </c>
       <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
         <v>1</v>
       </c>
-      <c r="AA70">
+      <c r="AD70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27">
+    <row r="71" spans="1:30">
       <c r="A71">
         <v>69</v>
       </c>
@@ -8332,12 +9235,6 @@
       <c r="S71">
         <v>0</v>
       </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
       <c r="V71">
         <v>0</v>
       </c>
@@ -8356,8 +9253,17 @@
       <c r="AA71">
         <v>0</v>
       </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="1:27" ht="37.5">
+    <row r="72" spans="1:30" ht="37.5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -8415,32 +9321,41 @@
       <c r="S72">
         <v>22</v>
       </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>0</v>
+      <c r="T72" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="U72" t="s">
+        <v>528</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
         <v>1</v>
       </c>
-      <c r="X72">
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
       <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:27">
+    <row r="73" spans="1:30">
       <c r="A73">
         <v>71</v>
       </c>
@@ -8498,14 +9413,14 @@
       <c r="S73">
         <v>22</v>
       </c>
-      <c r="T73">
-        <v>0</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
+      <c r="T73" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="U73" t="s">
+        <v>528</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -8522,8 +9437,17 @@
       <c r="AA73">
         <v>0</v>
       </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="1:27">
+    <row r="74" spans="1:30" ht="37.5">
       <c r="A74">
         <v>72</v>
       </c>
@@ -8581,14 +9505,14 @@
       <c r="S74">
         <v>22</v>
       </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <v>0</v>
+      <c r="T74" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="U74" t="s">
+        <v>528</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W74">
         <v>0</v>
@@ -8605,8 +9529,17 @@
       <c r="AA74">
         <v>0</v>
       </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="1:27">
+    <row r="75" spans="1:30">
       <c r="A75">
         <v>73</v>
       </c>
@@ -8664,14 +9597,14 @@
       <c r="S75">
         <v>22</v>
       </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
+      <c r="T75" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="U75" t="s">
+        <v>531</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W75">
         <v>0</v>
@@ -8688,8 +9621,17 @@
       <c r="AA75">
         <v>0</v>
       </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="1:27">
+    <row r="76" spans="1:30" ht="37.5">
       <c r="A76">
         <v>74</v>
       </c>
@@ -8747,14 +9689,14 @@
       <c r="S76">
         <v>22</v>
       </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
+      <c r="T76" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="U76" t="s">
+        <v>531</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -8771,8 +9713,17 @@
       <c r="AA76">
         <v>0</v>
       </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="1:27">
+    <row r="77" spans="1:30">
       <c r="A77">
         <v>75</v>
       </c>
@@ -8830,14 +9781,14 @@
       <c r="S77">
         <v>22</v>
       </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
+      <c r="T77" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="U77" t="s">
+        <v>528</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W77">
         <v>0</v>
@@ -8854,8 +9805,17 @@
       <c r="AA77">
         <v>0</v>
       </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
     </row>
-    <row r="78" spans="1:27" ht="37.5">
+    <row r="78" spans="1:30" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -8913,14 +9873,14 @@
       <c r="S78">
         <v>22</v>
       </c>
-      <c r="T78">
-        <v>0</v>
-      </c>
-      <c r="U78">
-        <v>0</v>
+      <c r="T78" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="U78" t="s">
+        <v>528</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W78">
         <v>0</v>
@@ -8937,8 +9897,17 @@
       <c r="AA78">
         <v>0</v>
       </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AC78">
+        <v>0</v>
+      </c>
+      <c r="AD78">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="1:27">
+    <row r="79" spans="1:30" ht="37.5">
       <c r="A79">
         <v>77</v>
       </c>
@@ -8996,14 +9965,14 @@
       <c r="S79">
         <v>22</v>
       </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-      <c r="U79">
-        <v>0</v>
+      <c r="T79" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="U79" t="s">
+        <v>531</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W79">
         <v>0</v>
@@ -9020,8 +9989,17 @@
       <c r="AA79">
         <v>0</v>
       </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79">
+        <v>0</v>
+      </c>
     </row>
-    <row r="80" spans="1:27">
+    <row r="80" spans="1:30">
       <c r="A80">
         <v>78</v>
       </c>
@@ -9079,14 +10057,14 @@
       <c r="S80">
         <v>22</v>
       </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
+      <c r="T80" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="U80" t="s">
+        <v>528</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W80">
         <v>0</v>
@@ -9103,8 +10081,17 @@
       <c r="AA80">
         <v>0</v>
       </c>
+      <c r="AB80">
+        <v>0</v>
+      </c>
+      <c r="AC80">
+        <v>0</v>
+      </c>
+      <c r="AD80">
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:27" ht="37.5">
+    <row r="81" spans="1:30" ht="56.25">
       <c r="A81">
         <v>79</v>
       </c>
@@ -9162,14 +10149,14 @@
       <c r="S81">
         <v>22</v>
       </c>
-      <c r="T81">
-        <v>0</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
+      <c r="T81" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="U81" t="s">
+        <v>531</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W81">
         <v>0</v>
@@ -9186,8 +10173,17 @@
       <c r="AA81">
         <v>0</v>
       </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81">
+        <v>0</v>
+      </c>
+      <c r="AD81">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="1:27">
+    <row r="82" spans="1:30">
       <c r="A82">
         <v>80</v>
       </c>
@@ -9245,14 +10241,14 @@
       <c r="S82">
         <v>22</v>
       </c>
-      <c r="T82">
-        <v>0</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
+      <c r="T82" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="U82" t="s">
+        <v>528</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W82">
         <v>0</v>
@@ -9269,8 +10265,17 @@
       <c r="AA82">
         <v>0</v>
       </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AC82">
+        <v>0</v>
+      </c>
+      <c r="AD82">
+        <v>0</v>
+      </c>
     </row>
-    <row r="83" spans="1:27" ht="37.5">
+    <row r="83" spans="1:30" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -9328,14 +10333,14 @@
       <c r="S83">
         <v>22</v>
       </c>
-      <c r="T83">
-        <v>0</v>
-      </c>
-      <c r="U83">
-        <v>0</v>
+      <c r="T83" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="U83" t="s">
+        <v>531</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W83">
         <v>0</v>
@@ -9352,8 +10357,17 @@
       <c r="AA83">
         <v>0</v>
       </c>
+      <c r="AB83">
+        <v>0</v>
+      </c>
+      <c r="AC83">
+        <v>0</v>
+      </c>
+      <c r="AD83">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="1:27">
+    <row r="84" spans="1:30">
       <c r="A84">
         <v>82</v>
       </c>
@@ -9411,14 +10425,14 @@
       <c r="S84">
         <v>22</v>
       </c>
-      <c r="T84">
-        <v>0</v>
-      </c>
-      <c r="U84">
-        <v>0</v>
+      <c r="T84" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="U84" t="s">
+        <v>528</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W84">
         <v>0</v>
@@ -9435,8 +10449,17 @@
       <c r="AA84">
         <v>0</v>
       </c>
+      <c r="AB84">
+        <v>0</v>
+      </c>
+      <c r="AC84">
+        <v>0</v>
+      </c>
+      <c r="AD84">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="1:27">
+    <row r="85" spans="1:30" ht="37.5">
       <c r="A85">
         <v>83</v>
       </c>
@@ -9494,14 +10517,14 @@
       <c r="S85">
         <v>22</v>
       </c>
-      <c r="T85">
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <v>0</v>
+      <c r="T85" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="U85" t="s">
+        <v>531</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W85">
         <v>0</v>
@@ -9518,8 +10541,17 @@
       <c r="AA85">
         <v>0</v>
       </c>
+      <c r="AB85">
+        <v>0</v>
+      </c>
+      <c r="AC85">
+        <v>0</v>
+      </c>
+      <c r="AD85">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="1:27">
+    <row r="86" spans="1:30">
       <c r="A86">
         <v>84</v>
       </c>
@@ -9577,14 +10609,14 @@
       <c r="S86">
         <v>22</v>
       </c>
-      <c r="T86">
-        <v>0</v>
-      </c>
-      <c r="U86">
-        <v>0</v>
+      <c r="T86" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="U86" t="s">
+        <v>528</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W86">
         <v>0</v>
@@ -9601,8 +10633,17 @@
       <c r="AA86">
         <v>0</v>
       </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AC86">
+        <v>0</v>
+      </c>
+      <c r="AD86">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="1:27">
+    <row r="87" spans="1:30" ht="37.5">
       <c r="A87">
         <v>85</v>
       </c>
@@ -9660,14 +10701,14 @@
       <c r="S87">
         <v>22</v>
       </c>
-      <c r="T87">
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <v>0</v>
+      <c r="T87" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="U87" t="s">
+        <v>531</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W87">
         <v>0</v>
@@ -9684,8 +10725,17 @@
       <c r="AA87">
         <v>0</v>
       </c>
+      <c r="AB87">
+        <v>0</v>
+      </c>
+      <c r="AC87">
+        <v>0</v>
+      </c>
+      <c r="AD87">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="1:27">
+    <row r="88" spans="1:30">
       <c r="A88">
         <v>86</v>
       </c>
@@ -9743,32 +10793,41 @@
       <c r="S88">
         <v>22</v>
       </c>
-      <c r="T88">
-        <v>0</v>
-      </c>
-      <c r="U88">
+      <c r="T88" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="U88" t="s">
+        <v>531</v>
+      </c>
+      <c r="V88">
+        <v>22</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88">
         <v>2</v>
       </c>
-      <c r="V88">
-        <v>0</v>
-      </c>
-      <c r="W88">
+      <c r="Y88">
+        <v>0</v>
+      </c>
+      <c r="Z88">
         <v>1</v>
       </c>
-      <c r="X88">
-        <v>0</v>
-      </c>
-      <c r="Y88">
-        <v>0</v>
-      </c>
-      <c r="Z88">
-        <v>0</v>
-      </c>
       <c r="AA88">
         <v>0</v>
       </c>
+      <c r="AB88">
+        <v>0</v>
+      </c>
+      <c r="AC88">
+        <v>0</v>
+      </c>
+      <c r="AD88">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="1:27">
+    <row r="89" spans="1:30" ht="37.5">
       <c r="A89">
         <v>87</v>
       </c>
@@ -9826,14 +10885,14 @@
       <c r="S89">
         <v>22</v>
       </c>
-      <c r="T89">
-        <v>0</v>
-      </c>
-      <c r="U89">
-        <v>0</v>
+      <c r="T89" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="U89" t="s">
+        <v>531</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W89">
         <v>0</v>
@@ -9850,8 +10909,17 @@
       <c r="AA89">
         <v>0</v>
       </c>
+      <c r="AB89">
+        <v>0</v>
+      </c>
+      <c r="AC89">
+        <v>0</v>
+      </c>
+      <c r="AD89">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="1:27">
+    <row r="90" spans="1:30">
       <c r="A90">
         <v>88</v>
       </c>
@@ -9859,15 +10927,6 @@
       <c r="I90" s="5"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="T90">
-        <v>0</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
       <c r="W90">
         <v>0</v>
       </c>
@@ -9883,8 +10942,17 @@
       <c r="AA90">
         <v>0</v>
       </c>
+      <c r="AB90">
+        <v>0</v>
+      </c>
+      <c r="AC90">
+        <v>0</v>
+      </c>
+      <c r="AD90">
+        <v>0</v>
+      </c>
     </row>
-    <row r="91" spans="1:27">
+    <row r="91" spans="1:30">
       <c r="A91">
         <v>89</v>
       </c>
@@ -9893,7 +10961,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="1:27">
+    <row r="92" spans="1:30">
       <c r="A92">
         <v>90</v>
       </c>
@@ -9902,7 +10970,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="1:27">
+    <row r="93" spans="1:30">
       <c r="A93">
         <v>91</v>
       </c>
@@ -9911,7 +10979,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="1:27">
+    <row r="94" spans="1:30">
       <c r="A94">
         <v>92</v>
       </c>
@@ -9920,7 +10988,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="1:27">
+    <row r="95" spans="1:30">
       <c r="A95">
         <v>93</v>
       </c>
@@ -9929,7 +10997,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="1:27">
+    <row r="96" spans="1:30">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D281EC90-03B6-4BAC-B540-8373AA234E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39AAFEA-72EE-45FC-A30C-43FFC2A164FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="698">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -2448,6 +2448,282 @@
   </si>
   <si>
     <t>но давай и дальше стараться, Иф.</t>
+  </si>
+  <si>
+    <t>messageGerman</t>
+  </si>
+  <si>
+    <t>speakerNameGerman</t>
+  </si>
+  <si>
+    <t>messageSizeGerman</t>
+  </si>
+  <si>
+    <t>Wo … wo bin ich …?</t>
+  </si>
+  <si>
+    <t>Du</t>
+  </si>
+  <si>
+    <t>Wie es scheint, bist du aufgewacht.</t>
+  </si>
+  <si>
+    <t>Mein Name ist Kaname.
+Ich bin dein Führer durch „Mumei“.</t>
+  </si>
+  <si>
+    <t>So heißt das riesige Labyrinth hier in der Ewigen Welt.</t>
+  </si>
+  <si>
+    <t>Du hast in der Welt der Lebenden eine „Sünde“ begangen und bist gestorben.
+Jeder, der gesündigt hat, wird hier in Mumei eingekerkert.</t>
+  </si>
+  <si>
+    <t>Mit anderen Worten: Du bist einer von ihnen.</t>
+  </si>
+  <si>
+    <t>Eine Sünde?</t>
+  </si>
+  <si>
+    <t>Genau. Eine sehr, sehr schwere Sünde.</t>
+  </si>
+  <si>
+    <t>Übrigens, weißt du noch deinen eigenen Namen?</t>
+  </si>
+  <si>
+    <t>Ähm … mein Name ist …</t>
+  </si>
+  <si>
+    <t>Hä …? Ich weiß es nicht …</t>
+  </si>
+  <si>
+    <t>Natürlich weißt du ihn nicht.</t>
+  </si>
+  <si>
+    <t>Dein Name wurde nämlich vernichtet, bevor du in dieses Labyrinth kamst.</t>
+  </si>
+  <si>
+    <t>Mein Name … vernichtet …?</t>
+  </si>
+  <si>
+    <t>Was soll das heißen?</t>
+  </si>
+  <si>
+    <t>Wessen Name in der Ewigen Welt vernichtet wurde,
+der kann sich nicht mehr selbst an ihn erinnern.</t>
+  </si>
+  <si>
+    <t>Was …</t>
+  </si>
+  <si>
+    <t>Und wer sich nicht an seinen Namen erinnern kann …</t>
+  </si>
+  <si>
+    <t>… wird unter allen erdenklichen Qualen
+für immer durch dieses Labyrinth irren.</t>
+  </si>
+  <si>
+    <t>Früher oder später wird es dir genauso ergehen.</t>
+  </si>
+  <si>
+    <t>Nein … das ist grausam …</t>
+  </si>
+  <si>
+    <t>Warum …?</t>
+  </si>
+  <si>
+    <t>Weil Sünder keinen Namen brauchen.</t>
+  </si>
+  <si>
+    <t>Aber keine Sorge.</t>
+  </si>
+  <si>
+    <t>Wenn du dich an deine Sünde aus der Welt der Lebenden erinnerst
+und aus diesem Labyrinth entkommst, verrate ich dir deinen Namen.</t>
+  </si>
+  <si>
+    <t>Dann musst du weder Qualen erleiden
+noch umherirren.</t>
+  </si>
+  <si>
+    <t>… Willst du von hier entkommen?</t>
+  </si>
+  <si>
+    <t>… Ich will entkommen.</t>
+  </si>
+  <si>
+    <t>Aber wie kann ich entkommen?</t>
+  </si>
+  <si>
+    <t>… Es gibt einen Weg.</t>
+  </si>
+  <si>
+    <t>Du musst dich meiner Prüfung stellen und sie bestehen.</t>
+  </si>
+  <si>
+    <t>Dann kannst du entkommen.</t>
+  </si>
+  <si>
+    <t>… Stellst du dich meiner Prüfung?</t>
+  </si>
+  <si>
+    <t>… Ich stelle mich ihr.</t>
+  </si>
+  <si>
+    <t>… Verstanden.
+Dann erkläre ich dir, worin die Prüfung besteht.</t>
+  </si>
+  <si>
+    <t>Um die Prüfung zu bestehen,
+musst du zwei Bedingungen erfüllen.</t>
+  </si>
+  <si>
+    <t>Erstens: Entkomme aus diesem Labyrinth.
+Zweitens: Erinnere dich an die Sünde, die du in der Welt der Lebenden begangen hast.</t>
+  </si>
+  <si>
+    <t>Ich erkläre dir, wie du aus diesem Labyrinth entkommst.</t>
+  </si>
+  <si>
+    <t>Um zu entkommen, musst du „Dokumente“ und „Mysteriöse Gegenstände“
+finden, die überall in diesem Labyrinth verborgen sind.</t>
+  </si>
+  <si>
+    <t>Zuerst besorgst du dir ein Dokument.
+Öffne zur Probe die Schublade direkt vor dir.</t>
+  </si>
+  <si>
+    <t>Sieh dir den Inhalt des Dokuments an, das du gerade genommen hast.</t>
+  </si>
+  <si>
+    <t>Als Nächstes besorgst du dir einen Mysteriösen Gegenstand.</t>
+  </si>
+  <si>
+    <t>Öffne die beiden Schubladen direkt vor dir.</t>
+  </si>
+  <si>
+    <t>Sieh dir die Mysteriösen Gegenstände an, die du gerade genommen hast.</t>
+  </si>
+  <si>
+    <t>Zum Schluss berührst du die „Blaue Kugel des Urteils“ dort hinten.</t>
+  </si>
+  <si>
+    <t>Wähle den Mysteriösen Gegenstand, der eng
+mit dem Inhalt des Dokuments zusammenhängt.</t>
+  </si>
+  <si>
+    <t>Damit ist die Erklärung der Prüfung beendet.
+Hast du noch Fragen?</t>
+  </si>
+  <si>
+    <t>Hä? Du erklärst mir nicht, welche Sünde ich begangen habe?</t>
+  </si>
+  <si>
+    <t>Nein.</t>
+  </si>
+  <si>
+    <t>Nichts da mit „Was“.</t>
+  </si>
+  <si>
+    <t>Wenn du wirklich bereust, was du getan hast,
+solltest du dich sofort an deine Sünde erinnern können.</t>
+  </si>
+  <si>
+    <t>Deshalb ist die Erklärung hiermit beendet.</t>
+  </si>
+  <si>
+    <t>Außerdem ist es ohne Namen unpraktisch,
+deshalb nenne ich dich vorläufig „IF“.</t>
+  </si>
+  <si>
+    <t>Das ist doch in Ordnung, oder?</t>
+  </si>
+  <si>
+    <t>Äh … j-ja …</t>
+  </si>
+  <si>
+    <t>Zum Schluss noch eine Warnung zu diesem Labyrinth.</t>
+  </si>
+  <si>
+    <t>Eine Warnung?</t>
+  </si>
+  <si>
+    <t>Lass dich niemals von den „Umherirrenden“ fangen.</t>
+  </si>
+  <si>
+    <t>Umherirrende?</t>
+  </si>
+  <si>
+    <t>Das sind die Ungeheuer, die in Mumei lauern.</t>
+  </si>
+  <si>
+    <t>IF, lass dich auf keinen Fall von diesen Ungeheuern fangen.</t>
+  </si>
+  <si>
+    <t>Verstanden?</t>
+  </si>
+  <si>
+    <t>… J-ja …</t>
+  </si>
+  <si>
+    <t>Also gut, dann beginnen wir mit der Prüfung.
+Geh bitte den Gang hinter dir entlang.</t>
+  </si>
+  <si>
+    <t>IF, ich bete dafür, dass du die Prüfung bestehst.</t>
+  </si>
+  <si>
+    <t>… Endlich … kann ich aus diesem Labyrinth entkommen …</t>
+  </si>
+  <si>
+    <t>Was … was ist das …?</t>
+  </si>
+  <si>
+    <t>Warum geht das Labyrinth immer noch weiter?!</t>
+  </si>
+  <si>
+    <t>Liegt das nicht auf der Hand?</t>
+  </si>
+  <si>
+    <t>Weil du noch nicht aus dem Labyrinth entkommen bist.</t>
+  </si>
+  <si>
+    <t>… Was heißt, ich bin nicht entkommen?</t>
+  </si>
+  <si>
+    <t>Ich habe doch die Dokumente und die
+Mysteriösen Gegenstände gesammelt!</t>
+  </si>
+  <si>
+    <t>Dachtest du etwa, das wäre schon alles?</t>
+  </si>
+  <si>
+    <t>Dokumente und Mysteriöse Gegenstände
+gibt es auch in anderen Bereichen.</t>
+  </si>
+  <si>
+    <t>Das … kann nicht sein …</t>
+  </si>
+  <si>
+    <t>Außerdem hast du dich noch nicht an deine Sünde erinnert, oder, IF?</t>
+  </si>
+  <si>
+    <t>… !</t>
+  </si>
+  <si>
+    <t>Deshalb ist die Prüfung noch nicht vorbei.</t>
+  </si>
+  <si>
+    <t>Nein …</t>
+  </si>
+  <si>
+    <t>Der wahre Schrecken von Mumei beginnt erst jetzt, IF.</t>
+  </si>
+  <si>
+    <t>Ich weiß, es wird hart,</t>
+  </si>
+  <si>
+    <t>aber lass uns weiter durchhalten, IF.</t>
   </si>
 </sst>
 </file>
@@ -2816,7 +3092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD102"/>
+  <dimension ref="A1:AG102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -2839,16 +3115,19 @@
     <col min="20" max="20" width="104.375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21.375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27.75" customWidth="1"/>
-    <col min="24" max="24" width="22.5" customWidth="1"/>
-    <col min="25" max="25" width="13.625" customWidth="1"/>
-    <col min="27" max="27" width="17.125" customWidth="1"/>
-    <col min="28" max="28" width="28.125" customWidth="1"/>
-    <col min="29" max="29" width="13.125" customWidth="1"/>
-    <col min="30" max="30" width="16" customWidth="1"/>
+    <col min="23" max="23" width="52.125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.75" customWidth="1"/>
+    <col min="27" max="27" width="22.5" customWidth="1"/>
+    <col min="28" max="28" width="13.625" customWidth="1"/>
+    <col min="30" max="30" width="17.125" customWidth="1"/>
+    <col min="31" max="31" width="28.125" customWidth="1"/>
+    <col min="32" max="32" width="13.125" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2916,31 +3195,40 @@
         <v>526</v>
       </c>
       <c r="W1" t="s">
+        <v>612</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>614</v>
+      </c>
+      <c r="Z1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AG1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:33">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2969,12 +3257,6 @@
       <c r="V2">
         <v>0</v>
       </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
       <c r="Y2">
         <v>0</v>
       </c>
@@ -2993,8 +3275,17 @@
       <c r="AD2">
         <v>0</v>
       </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:33">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3061,14 +3352,14 @@
       <c r="V3">
         <v>22</v>
       </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
+      <c r="W3" t="s">
+        <v>615</v>
+      </c>
+      <c r="X3" t="s">
+        <v>616</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3085,8 +3376,17 @@
       <c r="AD3">
         <v>0</v>
       </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:33">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3153,32 +3453,41 @@
       <c r="V4">
         <v>22</v>
       </c>
-      <c r="W4">
+      <c r="W4" t="s">
+        <v>617</v>
+      </c>
+      <c r="X4" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y4">
+        <v>22</v>
+      </c>
+      <c r="Z4">
         <v>1</v>
       </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
         <v>3</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
       <c r="AD4">
         <v>0</v>
       </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" ht="37.5">
+    <row r="5" spans="1:33" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3245,14 +3554,14 @@
       <c r="V5">
         <v>22</v>
       </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
+      <c r="W5" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="X5" t="s">
+        <v>34</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -3269,8 +3578,17 @@
       <c r="AD5">
         <v>0</v>
       </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:33">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3337,14 +3655,14 @@
       <c r="V6">
         <v>22</v>
       </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
+      <c r="W6" t="s">
+        <v>438</v>
+      </c>
+      <c r="X6" t="s">
+        <v>616</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -3361,8 +3679,17 @@
       <c r="AD6">
         <v>0</v>
       </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:33">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3429,14 +3756,14 @@
       <c r="V7">
         <v>22</v>
       </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
+      <c r="W7" t="s">
+        <v>619</v>
+      </c>
+      <c r="X7" t="s">
+        <v>34</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3453,8 +3780,17 @@
       <c r="AD7">
         <v>0</v>
       </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" ht="75">
+    <row r="8" spans="1:33" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3521,14 +3857,14 @@
       <c r="V8">
         <v>22</v>
       </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
+      <c r="W8" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="X8" t="s">
+        <v>34</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3545,8 +3881,17 @@
       <c r="AD8">
         <v>0</v>
       </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:33">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3613,14 +3958,14 @@
       <c r="V9">
         <v>22</v>
       </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
+      <c r="W9" t="s">
+        <v>621</v>
+      </c>
+      <c r="X9" t="s">
+        <v>34</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -3637,8 +3982,17 @@
       <c r="AD9">
         <v>0</v>
       </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:33">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3705,14 +4059,14 @@
       <c r="V10">
         <v>22</v>
       </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
+      <c r="W10" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="X10" t="s">
+        <v>616</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3729,8 +4083,17 @@
       <c r="AD10">
         <v>0</v>
       </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:33">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3797,14 +4160,14 @@
       <c r="V11">
         <v>22</v>
       </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
+      <c r="W11" t="s">
+        <v>623</v>
+      </c>
+      <c r="X11" t="s">
+        <v>34</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3821,8 +4184,17 @@
       <c r="AD11">
         <v>0</v>
       </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:33">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3889,14 +4261,14 @@
       <c r="V12">
         <v>22</v>
       </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
+      <c r="W12" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="X12" t="s">
+        <v>34</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3913,8 +4285,17 @@
       <c r="AD12">
         <v>0</v>
       </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:33">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3981,21 +4362,21 @@
       <c r="V13">
         <v>22</v>
       </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
+      <c r="W13" t="s">
+        <v>625</v>
+      </c>
+      <c r="X13" t="s">
+        <v>616</v>
+      </c>
+      <c r="Y13">
+        <v>22</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
         <v>1</v>
       </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
       <c r="AB13">
         <v>0</v>
       </c>
@@ -4005,8 +4386,17 @@
       <c r="AD13">
         <v>0</v>
       </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:33">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4073,14 +4463,14 @@
       <c r="V14">
         <v>22</v>
       </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
+      <c r="W14" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="X14" t="s">
+        <v>616</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -4097,8 +4487,17 @@
       <c r="AD14">
         <v>0</v>
       </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:33">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4165,14 +4564,14 @@
       <c r="V15">
         <v>22</v>
       </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
+      <c r="W15" t="s">
+        <v>627</v>
+      </c>
+      <c r="X15" t="s">
+        <v>34</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -4189,8 +4588,17 @@
       <c r="AD15">
         <v>0</v>
       </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:30" ht="56.25">
+    <row r="16" spans="1:33" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4257,14 +4665,14 @@
       <c r="V16">
         <v>22</v>
       </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
+      <c r="W16" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="X16" t="s">
+        <v>34</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -4281,8 +4689,17 @@
       <c r="AD16">
         <v>0</v>
       </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:30">
+    <row r="17" spans="1:33">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4349,14 +4766,14 @@
       <c r="V17">
         <v>22</v>
       </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
+      <c r="W17" t="s">
+        <v>629</v>
+      </c>
+      <c r="X17" t="s">
+        <v>616</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -4373,8 +4790,17 @@
       <c r="AD17">
         <v>0</v>
       </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:30">
+    <row r="18" spans="1:33">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4441,14 +4867,14 @@
       <c r="V18">
         <v>22</v>
       </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
+      <c r="W18" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="X18" t="s">
+        <v>616</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -4465,8 +4891,17 @@
       <c r="AD18">
         <v>0</v>
       </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:30" ht="56.25">
+    <row r="19" spans="1:33" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4533,14 +4968,14 @@
       <c r="V19">
         <v>22</v>
       </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
+      <c r="W19" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="X19" t="s">
+        <v>34</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -4557,8 +4992,17 @@
       <c r="AD19">
         <v>0</v>
       </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:33">
       <c r="A20">
         <v>18</v>
       </c>
@@ -4625,14 +5069,14 @@
       <c r="V20">
         <v>22</v>
       </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
+      <c r="W20" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="X20" t="s">
+        <v>616</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -4649,8 +5093,17 @@
       <c r="AD20">
         <v>0</v>
       </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:30" ht="37.5">
+    <row r="21" spans="1:33">
       <c r="A21">
         <v>19</v>
       </c>
@@ -4714,21 +5167,21 @@
       <c r="V21">
         <v>22</v>
       </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
+      <c r="W21" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="X21" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y21">
+        <v>22</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
         <v>1</v>
       </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
       <c r="AB21">
         <v>0</v>
       </c>
@@ -4738,8 +5191,17 @@
       <c r="AD21">
         <v>0</v>
       </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:30" ht="56.25">
+    <row r="22" spans="1:33" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -4806,14 +5268,14 @@
       <c r="V22">
         <v>22</v>
       </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
+      <c r="W22" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="X22" t="s">
+        <v>34</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -4830,8 +5292,17 @@
       <c r="AD22">
         <v>0</v>
       </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:30" ht="37.5">
+    <row r="23" spans="1:33" ht="37.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -4898,14 +5369,14 @@
       <c r="V23">
         <v>22</v>
       </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
+      <c r="W23" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="X23" t="s">
+        <v>34</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -4922,8 +5393,17 @@
       <c r="AD23">
         <v>0</v>
       </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:30">
+    <row r="24" spans="1:33">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4990,14 +5470,14 @@
       <c r="V24">
         <v>22</v>
       </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
+      <c r="W24" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="X24" t="s">
+        <v>616</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -5014,8 +5494,17 @@
       <c r="AD24">
         <v>0</v>
       </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:30">
+    <row r="25" spans="1:33">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5082,14 +5571,14 @@
       <c r="V25">
         <v>22</v>
       </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
+      <c r="W25" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="X25" t="s">
+        <v>616</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -5106,8 +5595,17 @@
       <c r="AD25">
         <v>0</v>
       </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:30" ht="37.5">
+    <row r="26" spans="1:33">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5174,14 +5672,14 @@
       <c r="V26">
         <v>22</v>
       </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
+      <c r="W26" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="X26" t="s">
+        <v>34</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -5198,8 +5696,17 @@
       <c r="AD26">
         <v>0</v>
       </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:30">
+    <row r="27" spans="1:33">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5266,14 +5773,14 @@
       <c r="V27">
         <v>22</v>
       </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
+      <c r="W27" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="X27" t="s">
+        <v>34</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -5290,8 +5797,17 @@
       <c r="AD27">
         <v>0</v>
       </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:30" ht="75">
+    <row r="28" spans="1:33" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5358,14 +5874,14 @@
       <c r="V28">
         <v>22</v>
       </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
+      <c r="W28" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="X28" t="s">
+        <v>34</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -5382,8 +5898,17 @@
       <c r="AD28">
         <v>0</v>
       </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:30" ht="56.25">
+    <row r="29" spans="1:33" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -5450,32 +5975,41 @@
       <c r="V29">
         <v>22</v>
       </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
+      <c r="W29" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="X29" t="s">
+        <v>34</v>
       </c>
       <c r="Y29">
+        <v>22</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
         <v>1</v>
       </c>
-      <c r="Z29">
+      <c r="AC29">
         <v>1</v>
       </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
       <c r="AD29">
         <v>0</v>
       </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:30">
+    <row r="30" spans="1:33">
       <c r="A30">
         <v>28</v>
       </c>
@@ -5542,14 +6076,14 @@
       <c r="V30">
         <v>22</v>
       </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
+      <c r="W30" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="X30" t="s">
+        <v>34</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -5566,8 +6100,17 @@
       <c r="AD30">
         <v>0</v>
       </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:30">
+    <row r="31" spans="1:33">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5634,14 +6177,14 @@
       <c r="V31">
         <v>22</v>
       </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
+      <c r="W31" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="X31" t="s">
+        <v>616</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -5658,8 +6201,17 @@
       <c r="AD31">
         <v>0</v>
       </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:30">
+    <row r="32" spans="1:33">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5726,14 +6278,14 @@
       <c r="V32">
         <v>22</v>
       </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
+      <c r="W32" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="X32" t="s">
+        <v>616</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -5750,8 +6302,17 @@
       <c r="AD32">
         <v>0</v>
       </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:30">
+    <row r="33" spans="1:33">
       <c r="A33">
         <v>31</v>
       </c>
@@ -5818,14 +6379,14 @@
       <c r="V33">
         <v>22</v>
       </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
+      <c r="W33" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="X33" t="s">
+        <v>34</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -5842,8 +6403,17 @@
       <c r="AD33">
         <v>0</v>
       </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:30" ht="37.5">
+    <row r="34" spans="1:33" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -5910,14 +6480,14 @@
       <c r="V34">
         <v>22</v>
       </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
+      <c r="W34" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="X34" t="s">
+        <v>34</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -5934,8 +6504,17 @@
       <c r="AD34">
         <v>0</v>
       </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:30">
+    <row r="35" spans="1:33">
       <c r="A35">
         <v>33</v>
       </c>
@@ -6002,32 +6581,41 @@
       <c r="V35">
         <v>22</v>
       </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
+      <c r="W35" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="X35" t="s">
+        <v>34</v>
       </c>
       <c r="Y35">
+        <v>22</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
         <v>1</v>
       </c>
-      <c r="Z35">
+      <c r="AC35">
         <v>1</v>
       </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
       <c r="AD35">
         <v>0</v>
       </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:30">
+    <row r="36" spans="1:33">
       <c r="A36">
         <v>34</v>
       </c>
@@ -6094,14 +6682,14 @@
       <c r="V36">
         <v>22</v>
       </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
+      <c r="W36" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="X36" t="s">
+        <v>34</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -6118,8 +6706,17 @@
       <c r="AD36">
         <v>0</v>
       </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:30">
+    <row r="37" spans="1:33">
       <c r="A37">
         <v>35</v>
       </c>
@@ -6186,14 +6783,14 @@
       <c r="V37">
         <v>22</v>
       </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
+      <c r="W37" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="X37" t="s">
+        <v>616</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -6210,8 +6807,17 @@
       <c r="AD37">
         <v>0</v>
       </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:30" ht="56.25">
+    <row r="38" spans="1:33" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -6278,32 +6884,41 @@
       <c r="V38">
         <v>22</v>
       </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
+      <c r="W38" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="X38" t="s">
+        <v>34</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z38">
         <v>0</v>
       </c>
       <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
         <v>1</v>
       </c>
-      <c r="AB38">
+      <c r="AE38">
         <v>9</v>
       </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
-      <c r="AD38">
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:30">
+    <row r="39" spans="1:33">
       <c r="A39">
         <v>37</v>
       </c>
@@ -6332,12 +6947,6 @@
       <c r="V39">
         <v>0</v>
       </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
       <c r="Y39">
         <v>0</v>
       </c>
@@ -6356,8 +6965,17 @@
       <c r="AD39">
         <v>0</v>
       </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:30" ht="56.25">
+    <row r="40" spans="1:33" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -6424,14 +7042,14 @@
       <c r="V40">
         <v>22</v>
       </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
+      <c r="W40" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="X40" t="s">
+        <v>34</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -6448,8 +7066,17 @@
       <c r="AD40">
         <v>0</v>
       </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:30" ht="85.5" customHeight="1">
+    <row r="41" spans="1:33" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -6516,14 +7143,14 @@
       <c r="V41">
         <v>22</v>
       </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
+      <c r="W41" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="X41" t="s">
+        <v>34</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -6540,8 +7167,17 @@
       <c r="AD41">
         <v>0</v>
       </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:30" ht="51.75" customHeight="1">
+    <row r="42" spans="1:33" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -6608,14 +7244,14 @@
       <c r="V42">
         <v>22</v>
       </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
+      <c r="W42" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="X42" t="s">
+        <v>34</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -6632,8 +7268,17 @@
       <c r="AD42">
         <v>0</v>
       </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:30" ht="93.75">
+    <row r="43" spans="1:33" ht="75">
       <c r="A43">
         <v>41</v>
       </c>
@@ -6700,14 +7345,14 @@
       <c r="V43">
         <v>22</v>
       </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
+      <c r="W43" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="X43" t="s">
+        <v>34</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -6724,8 +7369,17 @@
       <c r="AD43">
         <v>0</v>
       </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:30" ht="56.25">
+    <row r="44" spans="1:33" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -6792,32 +7446,41 @@
       <c r="V44">
         <v>22</v>
       </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>0</v>
+      <c r="W44" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="X44" t="s">
+        <v>34</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z44">
         <v>0</v>
       </c>
       <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
         <v>2</v>
       </c>
-      <c r="AB44">
+      <c r="AE44">
         <v>10</v>
       </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
-      <c r="AD44">
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="56.25">
+    <row r="45" spans="1:33" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -6884,32 +7547,41 @@
       <c r="V45">
         <v>22</v>
       </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>0</v>
+      <c r="W45" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="X45" t="s">
+        <v>34</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z45">
         <v>0</v>
       </c>
       <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
         <v>2</v>
       </c>
-      <c r="AB45">
+      <c r="AE45">
         <v>11</v>
       </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AD45">
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="37.5">
+    <row r="46" spans="1:33" ht="37.5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -6976,14 +7648,14 @@
       <c r="V46">
         <v>22</v>
       </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46">
-        <v>0</v>
+      <c r="W46" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="X46" t="s">
+        <v>34</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -7000,8 +7672,17 @@
       <c r="AD46">
         <v>0</v>
       </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:30" ht="37.5">
+    <row r="47" spans="1:33">
       <c r="A47">
         <v>45</v>
       </c>
@@ -7068,32 +7749,41 @@
       <c r="V47">
         <v>22</v>
       </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
+      <c r="W47" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="X47" t="s">
+        <v>34</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z47">
         <v>0</v>
       </c>
       <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
         <v>3</v>
       </c>
-      <c r="AB47">
+      <c r="AE47">
         <v>12</v>
       </c>
-      <c r="AC47">
-        <v>0</v>
-      </c>
-      <c r="AD47">
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="56.25">
+    <row r="48" spans="1:33" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -7160,32 +7850,41 @@
       <c r="V48">
         <v>22</v>
       </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
+      <c r="W48" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="X48" t="s">
+        <v>34</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z48">
         <v>0</v>
       </c>
       <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
         <v>2</v>
       </c>
-      <c r="AB48">
+      <c r="AE48">
         <v>13</v>
       </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="37.5">
+    <row r="49" spans="1:33" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -7252,14 +7951,14 @@
       <c r="V49">
         <v>22</v>
       </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
+      <c r="W49" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="X49" t="s">
+        <v>34</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -7276,8 +7975,17 @@
       <c r="AD49">
         <v>0</v>
       </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:30" ht="56.25">
+    <row r="50" spans="1:33" ht="56.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -7344,32 +8052,41 @@
       <c r="V50">
         <v>22</v>
       </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
+      <c r="W50" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="X50" t="s">
+        <v>34</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z50">
         <v>0</v>
       </c>
       <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
         <v>2</v>
       </c>
-      <c r="AB50">
+      <c r="AE50">
         <v>14</v>
       </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:30" ht="56.25">
+    <row r="51" spans="1:33" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -7436,14 +8153,14 @@
       <c r="V51">
         <v>22</v>
       </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
+      <c r="W51" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="X51" t="s">
+        <v>34</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -7460,8 +8177,17 @@
       <c r="AD51">
         <v>0</v>
       </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:30" ht="37.5">
+    <row r="52" spans="1:33" ht="37.5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -7528,14 +8254,14 @@
       <c r="V52">
         <v>22</v>
       </c>
-      <c r="W52">
-        <v>0</v>
-      </c>
-      <c r="X52">
-        <v>0</v>
+      <c r="W52" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="X52" t="s">
+        <v>616</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -7552,8 +8278,17 @@
       <c r="AD52">
         <v>0</v>
       </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:30">
+    <row r="53" spans="1:33">
       <c r="A53">
         <v>51</v>
       </c>
@@ -7620,14 +8355,14 @@
       <c r="V53">
         <v>22</v>
       </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53">
-        <v>0</v>
+      <c r="W53" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="X53" t="s">
+        <v>34</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -7644,8 +8379,17 @@
       <c r="AD53">
         <v>0</v>
       </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="1:30">
+    <row r="54" spans="1:33">
       <c r="A54">
         <v>52</v>
       </c>
@@ -7712,14 +8456,14 @@
       <c r="V54">
         <v>22</v>
       </c>
-      <c r="W54">
-        <v>0</v>
-      </c>
-      <c r="X54">
-        <v>0</v>
+      <c r="W54" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="X54" t="s">
+        <v>616</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -7736,8 +8480,17 @@
       <c r="AD54">
         <v>0</v>
       </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="1:30">
+    <row r="55" spans="1:33">
       <c r="A55">
         <v>53</v>
       </c>
@@ -7804,14 +8557,14 @@
       <c r="V55">
         <v>22</v>
       </c>
-      <c r="W55">
-        <v>0</v>
-      </c>
-      <c r="X55">
-        <v>0</v>
+      <c r="W55" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="X55" t="s">
+        <v>34</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -7828,8 +8581,17 @@
       <c r="AD55">
         <v>0</v>
       </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:30" ht="75">
+    <row r="56" spans="1:33" ht="56.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -7896,14 +8658,14 @@
       <c r="V56">
         <v>22</v>
       </c>
-      <c r="W56">
-        <v>0</v>
-      </c>
-      <c r="X56">
-        <v>0</v>
+      <c r="W56" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="X56" t="s">
+        <v>34</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -7920,8 +8682,17 @@
       <c r="AD56">
         <v>0</v>
       </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:30" ht="37.5">
+    <row r="57" spans="1:33">
       <c r="A57">
         <v>55</v>
       </c>
@@ -7988,14 +8759,14 @@
       <c r="V57">
         <v>22</v>
       </c>
-      <c r="W57">
-        <v>0</v>
-      </c>
-      <c r="X57">
-        <v>0</v>
+      <c r="W57" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="X57" t="s">
+        <v>34</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -8012,8 +8783,17 @@
       <c r="AD57">
         <v>0</v>
       </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:30" ht="56.25">
+    <row r="58" spans="1:33" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -8080,14 +8860,14 @@
       <c r="V58">
         <v>22</v>
       </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
+      <c r="W58" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="X58" t="s">
+        <v>34</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -8104,8 +8884,17 @@
       <c r="AD58">
         <v>0</v>
       </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="1:30">
+    <row r="59" spans="1:33">
       <c r="A59">
         <v>57</v>
       </c>
@@ -8172,14 +8961,14 @@
       <c r="V59">
         <v>22</v>
       </c>
-      <c r="W59">
-        <v>0</v>
-      </c>
-      <c r="X59">
-        <v>0</v>
+      <c r="W59" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="X59" t="s">
+        <v>34</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -8196,8 +8985,17 @@
       <c r="AD59">
         <v>0</v>
       </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="1:30">
+    <row r="60" spans="1:33">
       <c r="A60">
         <v>58</v>
       </c>
@@ -8264,14 +9062,14 @@
       <c r="V60">
         <v>22</v>
       </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
+      <c r="W60" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="X60" t="s">
+        <v>616</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -8288,8 +9086,17 @@
       <c r="AD60">
         <v>0</v>
       </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="1:30" ht="56.25">
+    <row r="61" spans="1:33" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -8356,14 +9163,14 @@
       <c r="V61">
         <v>22</v>
       </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
+      <c r="W61" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="X61" t="s">
+        <v>34</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -8380,8 +9187,17 @@
       <c r="AD61">
         <v>0</v>
       </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="1:30">
+    <row r="62" spans="1:33">
       <c r="A62">
         <v>60</v>
       </c>
@@ -8448,21 +9264,21 @@
       <c r="V62">
         <v>22</v>
       </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="X62">
+      <c r="W62" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="X62" t="s">
+        <v>616</v>
+      </c>
+      <c r="Y62">
+        <v>22</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
         <v>1</v>
       </c>
-      <c r="Y62">
-        <v>0</v>
-      </c>
-      <c r="Z62">
-        <v>0</v>
-      </c>
-      <c r="AA62">
-        <v>0</v>
-      </c>
       <c r="AB62">
         <v>0</v>
       </c>
@@ -8472,8 +9288,17 @@
       <c r="AD62">
         <v>0</v>
       </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="1:30" ht="37.5">
+    <row r="63" spans="1:33">
       <c r="A63">
         <v>61</v>
       </c>
@@ -8540,14 +9365,14 @@
       <c r="V63">
         <v>22</v>
       </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
+      <c r="W63" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="X63" t="s">
+        <v>34</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -8564,8 +9389,17 @@
       <c r="AD63">
         <v>0</v>
       </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="1:30">
+    <row r="64" spans="1:33">
       <c r="A64">
         <v>62</v>
       </c>
@@ -8632,14 +9466,14 @@
       <c r="V64">
         <v>22</v>
       </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
+      <c r="W64" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="X64" t="s">
+        <v>616</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -8656,8 +9490,17 @@
       <c r="AD64">
         <v>0</v>
       </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="1:30" ht="37.5">
+    <row r="65" spans="1:33">
       <c r="A65">
         <v>63</v>
       </c>
@@ -8724,14 +9567,14 @@
       <c r="V65">
         <v>22</v>
       </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
+      <c r="W65" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="X65" t="s">
+        <v>34</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -8748,8 +9591,17 @@
       <c r="AD65">
         <v>0</v>
       </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:30" ht="37.5">
+    <row r="66" spans="1:33" ht="37.5">
       <c r="A66">
         <v>64</v>
       </c>
@@ -8816,14 +9668,14 @@
       <c r="V66">
         <v>22</v>
       </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
+      <c r="W66" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="X66" t="s">
+        <v>34</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -8840,8 +9692,17 @@
       <c r="AD66">
         <v>0</v>
       </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="1:30">
+    <row r="67" spans="1:33">
       <c r="A67">
         <v>65</v>
       </c>
@@ -8908,14 +9769,14 @@
       <c r="V67">
         <v>22</v>
       </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
+      <c r="W67" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="X67" t="s">
+        <v>34</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -8932,8 +9793,17 @@
       <c r="AD67">
         <v>0</v>
       </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
     </row>
-    <row r="68" spans="1:30">
+    <row r="68" spans="1:33">
       <c r="A68">
         <v>66</v>
       </c>
@@ -9000,14 +9870,14 @@
       <c r="V68">
         <v>22</v>
       </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
+      <c r="W68" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="X68" t="s">
+        <v>616</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -9024,8 +9894,17 @@
       <c r="AD68">
         <v>0</v>
       </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="1:30" ht="56.25">
+    <row r="69" spans="1:33" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -9092,14 +9971,14 @@
       <c r="V69">
         <v>22</v>
       </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
+      <c r="W69" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="X69" t="s">
+        <v>34</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -9116,8 +9995,17 @@
       <c r="AD69">
         <v>0</v>
       </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="1:30" ht="37.5">
+    <row r="70" spans="1:33" ht="37.5">
       <c r="A70">
         <v>68</v>
       </c>
@@ -9184,14 +10072,14 @@
       <c r="V70">
         <v>22</v>
       </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
+      <c r="W70" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="X70" t="s">
+        <v>34</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -9203,13 +10091,22 @@
         <v>0</v>
       </c>
       <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
         <v>1</v>
       </c>
-      <c r="AD70">
+      <c r="AG70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:30">
+    <row r="71" spans="1:33">
       <c r="A71">
         <v>69</v>
       </c>
@@ -9238,12 +10135,6 @@
       <c r="V71">
         <v>0</v>
       </c>
-      <c r="W71">
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
       <c r="Y71">
         <v>0</v>
       </c>
@@ -9262,8 +10153,17 @@
       <c r="AD71">
         <v>0</v>
       </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="1:30" ht="37.5">
+    <row r="72" spans="1:33" ht="37.5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -9330,32 +10230,41 @@
       <c r="V72">
         <v>22</v>
       </c>
-      <c r="W72">
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <v>0</v>
+      <c r="W72" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="X72" t="s">
+        <v>616</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
         <v>1</v>
       </c>
-      <c r="AA72">
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <v>0</v>
-      </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
       <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:30">
+    <row r="73" spans="1:33">
       <c r="A73">
         <v>71</v>
       </c>
@@ -9422,14 +10331,14 @@
       <c r="V73">
         <v>22</v>
       </c>
-      <c r="W73">
-        <v>0</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
+      <c r="W73" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="X73" t="s">
+        <v>616</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -9446,8 +10355,17 @@
       <c r="AD73">
         <v>0</v>
       </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="1:30" ht="37.5">
+    <row r="74" spans="1:33">
       <c r="A74">
         <v>72</v>
       </c>
@@ -9514,14 +10432,14 @@
       <c r="V74">
         <v>22</v>
       </c>
-      <c r="W74">
-        <v>0</v>
-      </c>
-      <c r="X74">
-        <v>0</v>
+      <c r="W74" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="X74" t="s">
+        <v>616</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -9538,8 +10456,17 @@
       <c r="AD74">
         <v>0</v>
       </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="1:30">
+    <row r="75" spans="1:33">
       <c r="A75">
         <v>73</v>
       </c>
@@ -9606,14 +10533,14 @@
       <c r="V75">
         <v>22</v>
       </c>
-      <c r="W75">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>0</v>
+      <c r="W75" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="X75" t="s">
+        <v>34</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -9630,8 +10557,17 @@
       <c r="AD75">
         <v>0</v>
       </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="1:30" ht="37.5">
+    <row r="76" spans="1:33" ht="37.5">
       <c r="A76">
         <v>74</v>
       </c>
@@ -9698,14 +10634,14 @@
       <c r="V76">
         <v>22</v>
       </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76">
-        <v>0</v>
+      <c r="W76" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="X76" t="s">
+        <v>34</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -9722,8 +10658,17 @@
       <c r="AD76">
         <v>0</v>
       </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>0</v>
+      </c>
+      <c r="AG76">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="1:30">
+    <row r="77" spans="1:33">
       <c r="A77">
         <v>75</v>
       </c>
@@ -9790,14 +10735,14 @@
       <c r="V77">
         <v>22</v>
       </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <v>0</v>
+      <c r="W77" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="X77" t="s">
+        <v>616</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -9814,8 +10759,17 @@
       <c r="AD77">
         <v>0</v>
       </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+      <c r="AG77">
+        <v>0</v>
+      </c>
     </row>
-    <row r="78" spans="1:30" ht="37.5">
+    <row r="78" spans="1:33" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -9882,14 +10836,14 @@
       <c r="V78">
         <v>22</v>
       </c>
-      <c r="W78">
-        <v>0</v>
-      </c>
-      <c r="X78">
-        <v>0</v>
+      <c r="W78" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="X78" t="s">
+        <v>616</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -9906,8 +10860,17 @@
       <c r="AD78">
         <v>0</v>
       </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0</v>
+      </c>
+      <c r="AG78">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="1:30" ht="37.5">
+    <row r="79" spans="1:33">
       <c r="A79">
         <v>77</v>
       </c>
@@ -9974,14 +10937,14 @@
       <c r="V79">
         <v>22</v>
       </c>
-      <c r="W79">
-        <v>0</v>
-      </c>
-      <c r="X79">
-        <v>0</v>
+      <c r="W79" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="X79" t="s">
+        <v>34</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -9998,8 +10961,17 @@
       <c r="AD79">
         <v>0</v>
       </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>0</v>
+      </c>
+      <c r="AG79">
+        <v>0</v>
+      </c>
     </row>
-    <row r="80" spans="1:30">
+    <row r="80" spans="1:33">
       <c r="A80">
         <v>78</v>
       </c>
@@ -10066,14 +11038,14 @@
       <c r="V80">
         <v>22</v>
       </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
+      <c r="W80" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="X80" t="s">
+        <v>616</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -10090,8 +11062,17 @@
       <c r="AD80">
         <v>0</v>
       </c>
+      <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:30" ht="56.25">
+    <row r="81" spans="1:33" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -10158,14 +11139,14 @@
       <c r="V81">
         <v>22</v>
       </c>
-      <c r="W81">
-        <v>0</v>
-      </c>
-      <c r="X81">
-        <v>0</v>
+      <c r="W81" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="X81" t="s">
+        <v>34</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -10182,8 +11163,17 @@
       <c r="AD81">
         <v>0</v>
       </c>
+      <c r="AE81">
+        <v>0</v>
+      </c>
+      <c r="AF81">
+        <v>0</v>
+      </c>
+      <c r="AG81">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="1:30">
+    <row r="82" spans="1:33">
       <c r="A82">
         <v>80</v>
       </c>
@@ -10250,14 +11240,14 @@
       <c r="V82">
         <v>22</v>
       </c>
-      <c r="W82">
-        <v>0</v>
-      </c>
-      <c r="X82">
-        <v>0</v>
+      <c r="W82" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="X82" t="s">
+        <v>616</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -10274,8 +11264,17 @@
       <c r="AD82">
         <v>0</v>
       </c>
+      <c r="AE82">
+        <v>0</v>
+      </c>
+      <c r="AF82">
+        <v>0</v>
+      </c>
+      <c r="AG82">
+        <v>0</v>
+      </c>
     </row>
-    <row r="83" spans="1:30" ht="37.5">
+    <row r="83" spans="1:33" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -10342,14 +11341,14 @@
       <c r="V83">
         <v>22</v>
       </c>
-      <c r="W83">
-        <v>0</v>
-      </c>
-      <c r="X83">
-        <v>0</v>
+      <c r="W83" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="X83" t="s">
+        <v>34</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -10366,8 +11365,17 @@
       <c r="AD83">
         <v>0</v>
       </c>
+      <c r="AE83">
+        <v>0</v>
+      </c>
+      <c r="AF83">
+        <v>0</v>
+      </c>
+      <c r="AG83">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="1:30">
+    <row r="84" spans="1:33">
       <c r="A84">
         <v>82</v>
       </c>
@@ -10434,14 +11442,14 @@
       <c r="V84">
         <v>22</v>
       </c>
-      <c r="W84">
-        <v>0</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
+      <c r="W84" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="X84" t="s">
+        <v>616</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -10458,8 +11466,17 @@
       <c r="AD84">
         <v>0</v>
       </c>
+      <c r="AE84">
+        <v>0</v>
+      </c>
+      <c r="AF84">
+        <v>0</v>
+      </c>
+      <c r="AG84">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="1:30" ht="37.5">
+    <row r="85" spans="1:33">
       <c r="A85">
         <v>83</v>
       </c>
@@ -10526,14 +11543,14 @@
       <c r="V85">
         <v>22</v>
       </c>
-      <c r="W85">
-        <v>0</v>
-      </c>
-      <c r="X85">
-        <v>0</v>
+      <c r="W85" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="X85" t="s">
+        <v>34</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -10550,8 +11567,17 @@
       <c r="AD85">
         <v>0</v>
       </c>
+      <c r="AE85">
+        <v>0</v>
+      </c>
+      <c r="AF85">
+        <v>0</v>
+      </c>
+      <c r="AG85">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="1:30">
+    <row r="86" spans="1:33">
       <c r="A86">
         <v>84</v>
       </c>
@@ -10618,14 +11644,14 @@
       <c r="V86">
         <v>22</v>
       </c>
-      <c r="W86">
-        <v>0</v>
-      </c>
-      <c r="X86">
-        <v>0</v>
+      <c r="W86" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="X86" t="s">
+        <v>616</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -10642,8 +11668,17 @@
       <c r="AD86">
         <v>0</v>
       </c>
+      <c r="AE86">
+        <v>0</v>
+      </c>
+      <c r="AF86">
+        <v>0</v>
+      </c>
+      <c r="AG86">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="1:30" ht="37.5">
+    <row r="87" spans="1:33">
       <c r="A87">
         <v>85</v>
       </c>
@@ -10710,14 +11745,14 @@
       <c r="V87">
         <v>22</v>
       </c>
-      <c r="W87">
-        <v>0</v>
-      </c>
-      <c r="X87">
-        <v>0</v>
+      <c r="W87" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="X87" t="s">
+        <v>34</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -10734,8 +11769,17 @@
       <c r="AD87">
         <v>0</v>
       </c>
+      <c r="AE87">
+        <v>0</v>
+      </c>
+      <c r="AF87">
+        <v>0</v>
+      </c>
+      <c r="AG87">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="1:30">
+    <row r="88" spans="1:33">
       <c r="A88">
         <v>86</v>
       </c>
@@ -10802,32 +11846,41 @@
       <c r="V88">
         <v>22</v>
       </c>
-      <c r="W88">
-        <v>0</v>
-      </c>
-      <c r="X88">
+      <c r="W88" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="X88" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y88">
+        <v>22</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+      <c r="AA88">
         <v>2</v>
       </c>
-      <c r="Y88">
-        <v>0</v>
-      </c>
-      <c r="Z88">
+      <c r="AB88">
+        <v>0</v>
+      </c>
+      <c r="AC88">
         <v>1</v>
       </c>
-      <c r="AA88">
-        <v>0</v>
-      </c>
-      <c r="AB88">
-        <v>0</v>
-      </c>
-      <c r="AC88">
-        <v>0</v>
-      </c>
       <c r="AD88">
         <v>0</v>
       </c>
+      <c r="AE88">
+        <v>0</v>
+      </c>
+      <c r="AF88">
+        <v>0</v>
+      </c>
+      <c r="AG88">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="1:30" ht="37.5">
+    <row r="89" spans="1:33">
       <c r="A89">
         <v>87</v>
       </c>
@@ -10894,14 +11947,14 @@
       <c r="V89">
         <v>22</v>
       </c>
-      <c r="W89">
-        <v>0</v>
-      </c>
-      <c r="X89">
-        <v>0</v>
+      <c r="W89" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="X89" t="s">
+        <v>34</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -10918,8 +11971,17 @@
       <c r="AD89">
         <v>0</v>
       </c>
+      <c r="AE89">
+        <v>0</v>
+      </c>
+      <c r="AF89">
+        <v>0</v>
+      </c>
+      <c r="AG89">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="1:30">
+    <row r="90" spans="1:33">
       <c r="A90">
         <v>88</v>
       </c>
@@ -10927,15 +11989,6 @@
       <c r="I90" s="5"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="W90">
-        <v>0</v>
-      </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90">
-        <v>0</v>
-      </c>
       <c r="Z90">
         <v>0</v>
       </c>
@@ -10951,8 +12004,17 @@
       <c r="AD90">
         <v>0</v>
       </c>
+      <c r="AE90">
+        <v>0</v>
+      </c>
+      <c r="AF90">
+        <v>0</v>
+      </c>
+      <c r="AG90">
+        <v>0</v>
+      </c>
     </row>
-    <row r="91" spans="1:30">
+    <row r="91" spans="1:33">
       <c r="A91">
         <v>89</v>
       </c>
@@ -10961,7 +12023,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="1:30">
+    <row r="92" spans="1:33">
       <c r="A92">
         <v>90</v>
       </c>
@@ -10970,7 +12032,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="1:30">
+    <row r="93" spans="1:33">
       <c r="A93">
         <v>91</v>
       </c>
@@ -10979,7 +12041,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="1:30">
+    <row r="94" spans="1:33">
       <c r="A94">
         <v>92</v>
       </c>
@@ -10988,7 +12050,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="1:30">
+    <row r="95" spans="1:33">
       <c r="A95">
         <v>93</v>
       </c>
@@ -10997,7 +12059,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="1:30">
+    <row r="96" spans="1:33">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39AAFEA-72EE-45FC-A30C-43FFC2A164FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9A8526-432F-4158-A2D9-CCF5D90C32FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="785">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -2724,6 +2724,285 @@
   </si>
   <si>
     <t>aber lass uns weiter durchhalten, IF.</t>
+  </si>
+  <si>
+    <t>messageFrench</t>
+  </si>
+  <si>
+    <t>speakerNameFrench</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+  </si>
+  <si>
+    <t>Où… où suis-je ?</t>
+  </si>
+  <si>
+    <t>Vous</t>
+  </si>
+  <si>
+    <t>On dirait que tu es réveillé.</t>
+  </si>
+  <si>
+    <t>Je m'appelle Kaname.
+Je suis ton guide dans « Mumei ».</t>
+  </si>
+  <si>
+    <t>Mumei ?</t>
+  </si>
+  <si>
+    <t>C'est l'immense labyrinthe qui se trouve ici, dans le monde éternel.</t>
+  </si>
+  <si>
+    <t>Tu es mort dans le monde des vivants après avoir commis un « péché ».
+Tous ceux qui ont péché sont emprisonnés ici, dans Mumei.</t>
+  </si>
+  <si>
+    <t>Autrement dit, tu fais partie d'eux.</t>
+  </si>
+  <si>
+    <t>Un péché ?</t>
+  </si>
+  <si>
+    <t>Oui. Un péché très, très grave.</t>
+  </si>
+  <si>
+    <t>Au fait, tu te souviens de ton propre nom ?</t>
+  </si>
+  <si>
+    <t>Euh… mon nom, c'est…</t>
+  </si>
+  <si>
+    <t>Hein… Je ne sais pas…</t>
+  </si>
+  <si>
+    <t>C'est normal que tu ne t'en souviennes pas.</t>
+  </si>
+  <si>
+    <t>Car ton nom a été anéanti avant que tu n'arrives dans ce labyrinthe.</t>
+  </si>
+  <si>
+    <t>Mon nom… anéanti ?</t>
+  </si>
+  <si>
+    <t>Qu'est-ce que ça veut dire ?</t>
+  </si>
+  <si>
+    <t>Ceux dont le nom a été anéanti dans le monde éternel
+ne peuvent plus s'en souvenir par eux-mêmes.</t>
+  </si>
+  <si>
+    <t>Quoi…</t>
+  </si>
+  <si>
+    <t>Et ceux qui ne peuvent se souvenir de leur nom…</t>
+  </si>
+  <si>
+    <t>… erreront à jamais dans ce labyrinthe,
+en endurant toutes les souffrances.</t>
+  </si>
+  <si>
+    <t>Tôt ou tard, il en sera de même pour toi.</t>
+  </si>
+  <si>
+    <t>Non… c'est trop cruel…</t>
+  </si>
+  <si>
+    <t>Pourquoi…</t>
+  </si>
+  <si>
+    <t>Parce que les pécheurs n'ont pas besoin de nom.</t>
+  </si>
+  <si>
+    <t>Mais ne t'en fais pas.</t>
+  </si>
+  <si>
+    <t>Si tu te souviens du péché commis dans le monde des vivants
+et que tu t'échappes de ce labyrinthe, je te dirai ton nom.</t>
+  </si>
+  <si>
+    <t>Ainsi, tu n'auras plus à souffrir
+ni à errer.</t>
+  </si>
+  <si>
+    <t>… Veux-tu t'échapper d'ici ?</t>
+  </si>
+  <si>
+    <t>… Je veux m'échapper.</t>
+  </si>
+  <si>
+    <t>Mais comment faire pour s'échapper ?</t>
+  </si>
+  <si>
+    <t>… Il existe un moyen.</t>
+  </si>
+  <si>
+    <t>Relever mon épreuve et la surmonter.</t>
+  </si>
+  <si>
+    <t>Alors, tu pourras t'échapper.</t>
+  </si>
+  <si>
+    <t>… Acceptes-tu mon épreuve ?</t>
+  </si>
+  <si>
+    <t>… Je l'accepte.</t>
+  </si>
+  <si>
+    <t>… Très bien.
+Alors je vais t'expliquer en quoi consiste l'épreuve.</t>
+  </si>
+  <si>
+    <t>Pour surmonter l'épreuve,
+tu dois remplir deux conditions.</t>
+  </si>
+  <si>
+    <t>Un : t'échapper de ce labyrinthe.
+Deux : te souvenir du péché que tu as commis dans le monde des vivants.</t>
+  </si>
+  <si>
+    <t>Je vais t'expliquer comment t'échapper de ce labyrinthe.</t>
+  </si>
+  <si>
+    <t>Pour t'échapper, tu dois trouver des « Documents » et des « Objets mystérieux »
+cachés dans tous les recoins de ce labyrinthe.</t>
+  </si>
+  <si>
+    <t>D'abord, obtiens un Document.
+Pour essayer, ouvre le tiroir juste devant toi.</t>
+  </si>
+  <si>
+    <t>Regarde le contenu du Document que tu viens de prendre.</t>
+  </si>
+  <si>
+    <t>Ensuite, obtiens un Objet mystérieux.</t>
+  </si>
+  <si>
+    <t>Ouvre les deux tiroirs juste devant toi.</t>
+  </si>
+  <si>
+    <t>Examine les Objets mystérieux que tu viens de prendre.</t>
+  </si>
+  <si>
+    <t>Enfin, touche l'« Orbe bleu du Jugement » au fond.</t>
+  </si>
+  <si>
+    <t>Choisis l'Objet mystérieux étroitement lié
+au contenu du Document.</t>
+  </si>
+  <si>
+    <t>Voilà pour l'explication de l'épreuve.
+As-tu des questions ?</t>
+  </si>
+  <si>
+    <t>Hein ? Tu ne vas pas m'expliquer quel péché j'ai commis ?</t>
+  </si>
+  <si>
+    <t>Non.</t>
+  </si>
+  <si>
+    <t>Il n'y a pas de « quoi ».</t>
+  </si>
+  <si>
+    <t>Si tu regrettes vraiment ce que tu as fait,
+tu devrais pouvoir te souvenir de ton péché tout de suite.</t>
+  </si>
+  <si>
+    <t>C'est pourquoi l'explication s'arrête là.</t>
+  </si>
+  <si>
+    <t>Et puis, sans nom, ce n'est pas pratique,
+alors je vais t'appeler provisoirement « IF ».</t>
+  </si>
+  <si>
+    <t>Ça te va, n'est-ce pas ?</t>
+  </si>
+  <si>
+    <t>Euh… o-oui…</t>
+  </si>
+  <si>
+    <t>Pour finir, un avertissement important au sujet de ce labyrinthe.</t>
+  </si>
+  <si>
+    <t>Un avertissement ?</t>
+  </si>
+  <si>
+    <t>Ne te laisse jamais attraper par les « Errants ».</t>
+  </si>
+  <si>
+    <t>Les Errants ?</t>
+  </si>
+  <si>
+    <t>Ce sont les monstres qui rôdent dans Mumei.</t>
+  </si>
+  <si>
+    <t>IF, surtout, ne te laisse pas attraper par ces monstres.</t>
+  </si>
+  <si>
+    <t>Compris ?</t>
+  </si>
+  <si>
+    <t>… O-oui…</t>
+  </si>
+  <si>
+    <t>Bien, commençons l'épreuve.
+Avance dans le couloir derrière toi.</t>
+  </si>
+  <si>
+    <t>IF, je prie pour que tu réussisses l'épreuve.</t>
+  </si>
+  <si>
+    <t>… Enfin… je vais pouvoir m'échapper de ce labyrinthe…</t>
+  </si>
+  <si>
+    <t>Quoi… qu'est-ce que c'est…</t>
+  </si>
+  <si>
+    <t>Pourquoi le labyrinthe continue-t-il encore ?!</t>
+  </si>
+  <si>
+    <t>N'est-ce pas évident ?</t>
+  </si>
+  <si>
+    <t>Parce que tu ne t'es pas encore échappé du labyrinthe.</t>
+  </si>
+  <si>
+    <t>… Comment ça, pas échappé ?</t>
+  </si>
+  <si>
+    <t>J'ai pourtant rassemblé les Documents
+et les Objets mystérieux !</t>
+  </si>
+  <si>
+    <t>Tu croyais vraiment que c'était fini ?</t>
+  </si>
+  <si>
+    <t>Il y a aussi des Documents et des Objets mystérieux
+dans d'autres zones.</t>
+  </si>
+  <si>
+    <t>Ce n'est… pas possible…</t>
+  </si>
+  <si>
+    <t>En plus, IF, tu ne t'es toujours pas souvenu de ton péché, n'est-ce pas ?</t>
+  </si>
+  <si>
+    <t>… !</t>
+  </si>
+  <si>
+    <t>C'est pourquoi l'épreuve n'est pas encore terminée.</t>
+  </si>
+  <si>
+    <t>Non…</t>
+  </si>
+  <si>
+    <t>La véritable terreur de Mumei commence maintenant, IF.</t>
+  </si>
+  <si>
+    <t>Je sais que ce sera dur,</t>
+  </si>
+  <si>
+    <t>mais continuons à faire de notre mieux, IF.</t>
   </si>
 </sst>
 </file>
@@ -3092,7 +3371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG102"/>
+  <dimension ref="A1:AJ102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -3118,16 +3397,19 @@
     <col min="23" max="23" width="52.125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="21.125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="27.75" customWidth="1"/>
-    <col min="27" max="27" width="22.5" customWidth="1"/>
-    <col min="28" max="28" width="13.625" customWidth="1"/>
-    <col min="30" max="30" width="17.125" customWidth="1"/>
-    <col min="31" max="31" width="28.125" customWidth="1"/>
-    <col min="32" max="32" width="13.125" customWidth="1"/>
-    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="26" max="26" width="63.75" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="27.75" customWidth="1"/>
+    <col min="30" max="30" width="22.5" customWidth="1"/>
+    <col min="31" max="31" width="13.625" customWidth="1"/>
+    <col min="33" max="33" width="17.125" customWidth="1"/>
+    <col min="34" max="34" width="28.125" customWidth="1"/>
+    <col min="35" max="35" width="13.125" customWidth="1"/>
+    <col min="36" max="36" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3204,31 +3486,40 @@
         <v>614</v>
       </c>
       <c r="Z1" t="s">
+        <v>698</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>700</v>
+      </c>
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AH1" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AI1" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AJ1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:36">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3260,12 +3551,6 @@
       <c r="Y2">
         <v>0</v>
       </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
       <c r="AB2">
         <v>0</v>
       </c>
@@ -3284,8 +3569,17 @@
       <c r="AG2">
         <v>0</v>
       </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:36">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3361,14 +3655,14 @@
       <c r="Y3">
         <v>22</v>
       </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
+      <c r="Z3" t="s">
+        <v>701</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>702</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -3385,8 +3679,17 @@
       <c r="AG3">
         <v>0</v>
       </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:36">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3462,32 +3765,41 @@
       <c r="Y4">
         <v>22</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" t="s">
+        <v>703</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB4">
+        <v>22</v>
+      </c>
+      <c r="AC4">
         <v>1</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>3</v>
       </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
       <c r="AG4">
         <v>0</v>
       </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" ht="37.5">
+    <row r="5" spans="1:36" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3563,14 +3875,14 @@
       <c r="Y5">
         <v>22</v>
       </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
+      <c r="Z5" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>34</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -3587,8 +3899,17 @@
       <c r="AG5">
         <v>0</v>
       </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:36">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3664,14 +3985,14 @@
       <c r="Y6">
         <v>22</v>
       </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
+      <c r="Z6" t="s">
+        <v>705</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>702</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -3688,8 +4009,17 @@
       <c r="AG6">
         <v>0</v>
       </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:36">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3765,14 +4095,14 @@
       <c r="Y7">
         <v>22</v>
       </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
+      <c r="Z7" t="s">
+        <v>706</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>34</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -3789,8 +4119,17 @@
       <c r="AG7">
         <v>0</v>
       </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" ht="75">
+    <row r="8" spans="1:36" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3866,14 +4205,14 @@
       <c r="Y8">
         <v>22</v>
       </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
+      <c r="Z8" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>34</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -3890,8 +4229,17 @@
       <c r="AG8">
         <v>0</v>
       </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:36">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3967,14 +4315,14 @@
       <c r="Y9">
         <v>22</v>
       </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
+      <c r="Z9" t="s">
+        <v>708</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>34</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -3991,8 +4339,17 @@
       <c r="AG9">
         <v>0</v>
       </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:36">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4068,14 +4425,14 @@
       <c r="Y10">
         <v>22</v>
       </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
+      <c r="Z10" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>702</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -4092,8 +4449,17 @@
       <c r="AG10">
         <v>0</v>
       </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:36">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4169,14 +4535,14 @@
       <c r="Y11">
         <v>22</v>
       </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
+      <c r="Z11" t="s">
+        <v>710</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>34</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -4193,8 +4559,17 @@
       <c r="AG11">
         <v>0</v>
       </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:36">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4270,14 +4645,14 @@
       <c r="Y12">
         <v>22</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
+      <c r="Z12" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>34</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -4294,8 +4669,17 @@
       <c r="AG12">
         <v>0</v>
       </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:36">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4371,21 +4755,21 @@
       <c r="Y13">
         <v>22</v>
       </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
+      <c r="Z13" t="s">
+        <v>712</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>702</v>
+      </c>
+      <c r="AB13">
+        <v>22</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
         <v>1</v>
       </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
       <c r="AE13">
         <v>0</v>
       </c>
@@ -4395,8 +4779,17 @@
       <c r="AG13">
         <v>0</v>
       </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:36">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4472,14 +4865,14 @@
       <c r="Y14">
         <v>22</v>
       </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
+      <c r="Z14" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>702</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -4496,8 +4889,17 @@
       <c r="AG14">
         <v>0</v>
       </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:36">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4573,14 +4975,14 @@
       <c r="Y15">
         <v>22</v>
       </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
+      <c r="Z15" t="s">
+        <v>714</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>34</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -4597,8 +4999,17 @@
       <c r="AG15">
         <v>0</v>
       </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" ht="37.5">
+    <row r="16" spans="1:36" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4674,14 +5085,14 @@
       <c r="Y16">
         <v>22</v>
       </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
+      <c r="Z16" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>34</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -4698,8 +5109,17 @@
       <c r="AG16">
         <v>0</v>
       </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:36">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4775,14 +5195,14 @@
       <c r="Y17">
         <v>22</v>
       </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
+      <c r="Z17" t="s">
+        <v>716</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>702</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -4799,8 +5219,17 @@
       <c r="AG17">
         <v>0</v>
       </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:36">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4876,14 +5305,14 @@
       <c r="Y18">
         <v>22</v>
       </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
+      <c r="Z18" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>702</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -4900,8 +5329,17 @@
       <c r="AG18">
         <v>0</v>
       </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:33" ht="56.25">
+    <row r="19" spans="1:36" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4977,14 +5415,14 @@
       <c r="Y19">
         <v>22</v>
       </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
+      <c r="Z19" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>34</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -5001,8 +5439,17 @@
       <c r="AG19">
         <v>0</v>
       </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:36">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5078,14 +5525,14 @@
       <c r="Y20">
         <v>22</v>
       </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
+      <c r="Z20" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>702</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -5102,8 +5549,17 @@
       <c r="AG20">
         <v>0</v>
       </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:36">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5176,21 +5632,21 @@
       <c r="Y21">
         <v>22</v>
       </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
+      <c r="Z21" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB21">
+        <v>22</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
         <v>1</v>
       </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
       <c r="AE21">
         <v>0</v>
       </c>
@@ -5200,8 +5656,17 @@
       <c r="AG21">
         <v>0</v>
       </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:33" ht="37.5">
+    <row r="22" spans="1:36" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5277,14 +5742,14 @@
       <c r="Y22">
         <v>22</v>
       </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
+      <c r="Z22" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>34</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -5301,8 +5766,17 @@
       <c r="AG22">
         <v>0</v>
       </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:33" ht="37.5">
+    <row r="23" spans="1:36" ht="37.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5378,14 +5852,14 @@
       <c r="Y23">
         <v>22</v>
       </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
+      <c r="Z23" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>34</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -5402,8 +5876,17 @@
       <c r="AG23">
         <v>0</v>
       </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:36">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5479,14 +5962,14 @@
       <c r="Y24">
         <v>22</v>
       </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
+      <c r="Z24" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>702</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -5503,8 +5986,17 @@
       <c r="AG24">
         <v>0</v>
       </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:36">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5580,14 +6072,14 @@
       <c r="Y25">
         <v>22</v>
       </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
+      <c r="Z25" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>702</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -5604,8 +6096,17 @@
       <c r="AG25">
         <v>0</v>
       </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:36">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5681,14 +6182,14 @@
       <c r="Y26">
         <v>22</v>
       </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
+      <c r="Z26" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>34</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -5705,8 +6206,17 @@
       <c r="AG26">
         <v>0</v>
       </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:36">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5782,14 +6292,14 @@
       <c r="Y27">
         <v>22</v>
       </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
+      <c r="Z27" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>34</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -5806,8 +6316,17 @@
       <c r="AG27">
         <v>0</v>
       </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:33" ht="75">
+    <row r="28" spans="1:36" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5883,14 +6402,14 @@
       <c r="Y28">
         <v>22</v>
       </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
+      <c r="Z28" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>34</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5907,8 +6426,17 @@
       <c r="AG28">
         <v>0</v>
       </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:33" ht="37.5">
+    <row r="29" spans="1:36" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -5984,32 +6512,41 @@
       <c r="Y29">
         <v>22</v>
       </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
+      <c r="Z29" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>34</v>
       </c>
       <c r="AB29">
+        <v>22</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
         <v>1</v>
       </c>
-      <c r="AC29">
+      <c r="AF29">
         <v>1</v>
       </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
       <c r="AG29">
         <v>0</v>
       </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:36">
       <c r="A30">
         <v>28</v>
       </c>
@@ -6085,14 +6622,14 @@
       <c r="Y30">
         <v>22</v>
       </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
+      <c r="Z30" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>34</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -6109,8 +6646,17 @@
       <c r="AG30">
         <v>0</v>
       </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:36">
       <c r="A31">
         <v>29</v>
       </c>
@@ -6186,14 +6732,14 @@
       <c r="Y31">
         <v>22</v>
       </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
+      <c r="Z31" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>702</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -6210,8 +6756,17 @@
       <c r="AG31">
         <v>0</v>
       </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:36">
       <c r="A32">
         <v>30</v>
       </c>
@@ -6287,14 +6842,14 @@
       <c r="Y32">
         <v>22</v>
       </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
+      <c r="Z32" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>702</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -6311,8 +6866,17 @@
       <c r="AG32">
         <v>0</v>
       </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:36">
       <c r="A33">
         <v>31</v>
       </c>
@@ -6388,14 +6952,14 @@
       <c r="Y33">
         <v>22</v>
       </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
+      <c r="Z33" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>34</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -6412,8 +6976,17 @@
       <c r="AG33">
         <v>0</v>
       </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:33" ht="37.5">
+    <row r="34" spans="1:36" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -6489,14 +7062,14 @@
       <c r="Y34">
         <v>22</v>
       </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
+      <c r="Z34" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>34</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6513,8 +7086,17 @@
       <c r="AG34">
         <v>0</v>
       </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:36">
       <c r="A35">
         <v>33</v>
       </c>
@@ -6590,32 +7172,41 @@
       <c r="Y35">
         <v>22</v>
       </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
+      <c r="Z35" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>34</v>
       </c>
       <c r="AB35">
+        <v>22</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
         <v>1</v>
       </c>
-      <c r="AC35">
+      <c r="AF35">
         <v>1</v>
       </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
       <c r="AG35">
         <v>0</v>
       </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:36">
       <c r="A36">
         <v>34</v>
       </c>
@@ -6691,14 +7282,14 @@
       <c r="Y36">
         <v>22</v>
       </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
+      <c r="Z36" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>34</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6715,8 +7306,17 @@
       <c r="AG36">
         <v>0</v>
       </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:36">
       <c r="A37">
         <v>35</v>
       </c>
@@ -6792,14 +7392,14 @@
       <c r="Y37">
         <v>22</v>
       </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
+      <c r="Z37" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>702</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6816,8 +7416,17 @@
       <c r="AG37">
         <v>0</v>
       </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:33" ht="37.5">
+    <row r="38" spans="1:36" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -6893,32 +7502,41 @@
       <c r="Y38">
         <v>22</v>
       </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
-      <c r="AA38">
-        <v>0</v>
+      <c r="Z38" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>34</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC38">
         <v>0</v>
       </c>
       <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
         <v>1</v>
       </c>
-      <c r="AE38">
+      <c r="AH38">
         <v>9</v>
       </c>
-      <c r="AF38">
-        <v>0</v>
-      </c>
-      <c r="AG38">
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:33">
+    <row r="39" spans="1:36">
       <c r="A39">
         <v>37</v>
       </c>
@@ -6950,12 +7568,6 @@
       <c r="Y39">
         <v>0</v>
       </c>
-      <c r="Z39">
-        <v>0</v>
-      </c>
-      <c r="AA39">
-        <v>0</v>
-      </c>
       <c r="AB39">
         <v>0</v>
       </c>
@@ -6974,8 +7586,17 @@
       <c r="AG39">
         <v>0</v>
       </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:33" ht="37.5">
+    <row r="40" spans="1:36" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -7051,14 +7672,14 @@
       <c r="Y40">
         <v>22</v>
       </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>0</v>
+      <c r="Z40" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>34</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -7075,8 +7696,17 @@
       <c r="AG40">
         <v>0</v>
       </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:33" ht="85.5" customHeight="1">
+    <row r="41" spans="1:36" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -7152,14 +7782,14 @@
       <c r="Y41">
         <v>22</v>
       </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <v>0</v>
+      <c r="Z41" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>34</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7176,8 +7806,17 @@
       <c r="AG41">
         <v>0</v>
       </c>
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:33" ht="51.75" customHeight="1">
+    <row r="42" spans="1:36" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -7253,14 +7892,14 @@
       <c r="Y42">
         <v>22</v>
       </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>0</v>
+      <c r="Z42" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>34</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7277,8 +7916,17 @@
       <c r="AG42">
         <v>0</v>
       </c>
+      <c r="AH42">
+        <v>0</v>
+      </c>
+      <c r="AI42">
+        <v>0</v>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:33" ht="75">
+    <row r="43" spans="1:36" ht="56.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -7354,14 +8002,14 @@
       <c r="Y43">
         <v>22</v>
       </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
+      <c r="Z43" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>34</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7378,8 +8026,17 @@
       <c r="AG43">
         <v>0</v>
       </c>
+      <c r="AH43">
+        <v>0</v>
+      </c>
+      <c r="AI43">
+        <v>0</v>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:33" ht="37.5">
+    <row r="44" spans="1:36" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -7455,32 +8112,41 @@
       <c r="Y44">
         <v>22</v>
       </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>0</v>
+      <c r="Z44" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>34</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC44">
         <v>0</v>
       </c>
       <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
         <v>2</v>
       </c>
-      <c r="AE44">
+      <c r="AH44">
         <v>10</v>
       </c>
-      <c r="AF44">
-        <v>0</v>
-      </c>
-      <c r="AG44">
+      <c r="AI44">
+        <v>0</v>
+      </c>
+      <c r="AJ44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="56.25">
+    <row r="45" spans="1:36" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -7556,32 +8222,41 @@
       <c r="Y45">
         <v>22</v>
       </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45">
-        <v>0</v>
+      <c r="Z45" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>34</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC45">
         <v>0</v>
       </c>
       <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
         <v>2</v>
       </c>
-      <c r="AE45">
+      <c r="AH45">
         <v>11</v>
       </c>
-      <c r="AF45">
-        <v>0</v>
-      </c>
-      <c r="AG45">
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="37.5">
+    <row r="46" spans="1:36" ht="37.5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -7657,14 +8332,14 @@
       <c r="Y46">
         <v>22</v>
       </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-      <c r="AA46">
-        <v>0</v>
+      <c r="Z46" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>34</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -7681,8 +8356,17 @@
       <c r="AG46">
         <v>0</v>
       </c>
+      <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
+        <v>0</v>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:33">
+    <row r="47" spans="1:36">
       <c r="A47">
         <v>45</v>
       </c>
@@ -7758,32 +8442,41 @@
       <c r="Y47">
         <v>22</v>
       </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-      <c r="AA47">
-        <v>0</v>
+      <c r="Z47" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>34</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC47">
         <v>0</v>
       </c>
       <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
         <v>3</v>
       </c>
-      <c r="AE47">
+      <c r="AH47">
         <v>12</v>
       </c>
-      <c r="AF47">
-        <v>0</v>
-      </c>
-      <c r="AG47">
+      <c r="AI47">
+        <v>0</v>
+      </c>
+      <c r="AJ47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="37.5">
+    <row r="48" spans="1:36" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -7859,32 +8552,41 @@
       <c r="Y48">
         <v>22</v>
       </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
+      <c r="Z48" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>34</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC48">
         <v>0</v>
       </c>
       <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
         <v>2</v>
       </c>
-      <c r="AE48">
+      <c r="AH48">
         <v>13</v>
       </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
+      <c r="AI48">
+        <v>0</v>
+      </c>
+      <c r="AJ48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="37.5">
+    <row r="49" spans="1:36" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -7960,14 +8662,14 @@
       <c r="Y49">
         <v>22</v>
       </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
+      <c r="Z49" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>34</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -7984,8 +8686,17 @@
       <c r="AG49">
         <v>0</v>
       </c>
+      <c r="AH49">
+        <v>0</v>
+      </c>
+      <c r="AI49">
+        <v>0</v>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:33" ht="56.25">
+    <row r="50" spans="1:36" ht="56.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -8061,32 +8772,41 @@
       <c r="Y50">
         <v>22</v>
       </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
+      <c r="Z50" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>34</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC50">
         <v>0</v>
       </c>
       <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
         <v>2</v>
       </c>
-      <c r="AE50">
+      <c r="AH50">
         <v>14</v>
       </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
+      <c r="AI50">
+        <v>0</v>
+      </c>
+      <c r="AJ50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="37.5">
+    <row r="51" spans="1:36" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -8162,14 +8882,14 @@
       <c r="Y51">
         <v>22</v>
       </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <v>0</v>
+      <c r="Z51" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>34</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8186,8 +8906,17 @@
       <c r="AG51">
         <v>0</v>
       </c>
+      <c r="AH51">
+        <v>0</v>
+      </c>
+      <c r="AI51">
+        <v>0</v>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:33" ht="37.5">
+    <row r="52" spans="1:36" ht="37.5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -8263,14 +8992,14 @@
       <c r="Y52">
         <v>22</v>
       </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-      <c r="AA52">
-        <v>0</v>
+      <c r="Z52" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>702</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8287,8 +9016,17 @@
       <c r="AG52">
         <v>0</v>
       </c>
+      <c r="AH52">
+        <v>0</v>
+      </c>
+      <c r="AI52">
+        <v>0</v>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:36">
       <c r="A53">
         <v>51</v>
       </c>
@@ -8364,14 +9102,14 @@
       <c r="Y53">
         <v>22</v>
       </c>
-      <c r="Z53">
-        <v>0</v>
-      </c>
-      <c r="AA53">
-        <v>0</v>
+      <c r="Z53" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>34</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -8388,8 +9126,17 @@
       <c r="AG53">
         <v>0</v>
       </c>
+      <c r="AH53">
+        <v>0</v>
+      </c>
+      <c r="AI53">
+        <v>0</v>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:36">
       <c r="A54">
         <v>52</v>
       </c>
@@ -8465,14 +9212,14 @@
       <c r="Y54">
         <v>22</v>
       </c>
-      <c r="Z54">
-        <v>0</v>
-      </c>
-      <c r="AA54">
-        <v>0</v>
+      <c r="Z54" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>702</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -8489,8 +9236,17 @@
       <c r="AG54">
         <v>0</v>
       </c>
+      <c r="AH54">
+        <v>0</v>
+      </c>
+      <c r="AI54">
+        <v>0</v>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:36">
       <c r="A55">
         <v>53</v>
       </c>
@@ -8566,14 +9322,14 @@
       <c r="Y55">
         <v>22</v>
       </c>
-      <c r="Z55">
-        <v>0</v>
-      </c>
-      <c r="AA55">
-        <v>0</v>
+      <c r="Z55" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>34</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -8590,8 +9346,17 @@
       <c r="AG55">
         <v>0</v>
       </c>
+      <c r="AH55">
+        <v>0</v>
+      </c>
+      <c r="AI55">
+        <v>0</v>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:33" ht="56.25">
+    <row r="56" spans="1:36" ht="56.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -8667,14 +9432,14 @@
       <c r="Y56">
         <v>22</v>
       </c>
-      <c r="Z56">
-        <v>0</v>
-      </c>
-      <c r="AA56">
-        <v>0</v>
+      <c r="Z56" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>34</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -8691,8 +9456,17 @@
       <c r="AG56">
         <v>0</v>
       </c>
+      <c r="AH56">
+        <v>0</v>
+      </c>
+      <c r="AI56">
+        <v>0</v>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:36">
       <c r="A57">
         <v>55</v>
       </c>
@@ -8768,14 +9542,14 @@
       <c r="Y57">
         <v>22</v>
       </c>
-      <c r="Z57">
-        <v>0</v>
-      </c>
-      <c r="AA57">
-        <v>0</v>
+      <c r="Z57" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>34</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -8792,8 +9566,17 @@
       <c r="AG57">
         <v>0</v>
       </c>
+      <c r="AH57">
+        <v>0</v>
+      </c>
+      <c r="AI57">
+        <v>0</v>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:33" ht="37.5">
+    <row r="58" spans="1:36" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -8869,14 +9652,14 @@
       <c r="Y58">
         <v>22</v>
       </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-      <c r="AA58">
-        <v>0</v>
+      <c r="Z58" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>34</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -8893,8 +9676,17 @@
       <c r="AG58">
         <v>0</v>
       </c>
+      <c r="AH58">
+        <v>0</v>
+      </c>
+      <c r="AI58">
+        <v>0</v>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:36">
       <c r="A59">
         <v>57</v>
       </c>
@@ -8970,14 +9762,14 @@
       <c r="Y59">
         <v>22</v>
       </c>
-      <c r="Z59">
-        <v>0</v>
-      </c>
-      <c r="AA59">
-        <v>0</v>
+      <c r="Z59" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>34</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -8994,8 +9786,17 @@
       <c r="AG59">
         <v>0</v>
       </c>
+      <c r="AH59">
+        <v>0</v>
+      </c>
+      <c r="AI59">
+        <v>0</v>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:36">
       <c r="A60">
         <v>58</v>
       </c>
@@ -9071,14 +9872,14 @@
       <c r="Y60">
         <v>22</v>
       </c>
-      <c r="Z60">
-        <v>0</v>
-      </c>
-      <c r="AA60">
-        <v>0</v>
+      <c r="Z60" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>702</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -9095,8 +9896,17 @@
       <c r="AG60">
         <v>0</v>
       </c>
+      <c r="AH60">
+        <v>0</v>
+      </c>
+      <c r="AI60">
+        <v>0</v>
+      </c>
+      <c r="AJ60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="1:33" ht="37.5">
+    <row r="61" spans="1:36" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -9172,14 +9982,14 @@
       <c r="Y61">
         <v>22</v>
       </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <v>0</v>
+      <c r="Z61" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>34</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC61">
         <v>0</v>
@@ -9196,8 +10006,17 @@
       <c r="AG61">
         <v>0</v>
       </c>
+      <c r="AH61">
+        <v>0</v>
+      </c>
+      <c r="AI61">
+        <v>0</v>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="1:33">
+    <row r="62" spans="1:36">
       <c r="A62">
         <v>60</v>
       </c>
@@ -9273,21 +10092,21 @@
       <c r="Y62">
         <v>22</v>
       </c>
-      <c r="Z62">
-        <v>0</v>
-      </c>
-      <c r="AA62">
+      <c r="Z62" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>702</v>
+      </c>
+      <c r="AB62">
+        <v>22</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
         <v>1</v>
       </c>
-      <c r="AB62">
-        <v>0</v>
-      </c>
-      <c r="AC62">
-        <v>0</v>
-      </c>
-      <c r="AD62">
-        <v>0</v>
-      </c>
       <c r="AE62">
         <v>0</v>
       </c>
@@ -9297,8 +10116,17 @@
       <c r="AG62">
         <v>0</v>
       </c>
+      <c r="AH62">
+        <v>0</v>
+      </c>
+      <c r="AI62">
+        <v>0</v>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:36">
       <c r="A63">
         <v>61</v>
       </c>
@@ -9374,14 +10202,14 @@
       <c r="Y63">
         <v>22</v>
       </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
+      <c r="Z63" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>34</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -9398,8 +10226,17 @@
       <c r="AG63">
         <v>0</v>
       </c>
+      <c r="AH63">
+        <v>0</v>
+      </c>
+      <c r="AI63">
+        <v>0</v>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="1:33">
+    <row r="64" spans="1:36">
       <c r="A64">
         <v>62</v>
       </c>
@@ -9475,14 +10312,14 @@
       <c r="Y64">
         <v>22</v>
       </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
+      <c r="Z64" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>702</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -9499,8 +10336,17 @@
       <c r="AG64">
         <v>0</v>
       </c>
+      <c r="AH64">
+        <v>0</v>
+      </c>
+      <c r="AI64">
+        <v>0</v>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="1:33">
+    <row r="65" spans="1:36">
       <c r="A65">
         <v>63</v>
       </c>
@@ -9576,14 +10422,14 @@
       <c r="Y65">
         <v>22</v>
       </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
+      <c r="Z65" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>34</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -9600,8 +10446,17 @@
       <c r="AG65">
         <v>0</v>
       </c>
+      <c r="AH65">
+        <v>0</v>
+      </c>
+      <c r="AI65">
+        <v>0</v>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:33" ht="37.5">
+    <row r="66" spans="1:36" ht="37.5">
       <c r="A66">
         <v>64</v>
       </c>
@@ -9677,14 +10532,14 @@
       <c r="Y66">
         <v>22</v>
       </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
+      <c r="Z66" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>34</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -9701,8 +10556,17 @@
       <c r="AG66">
         <v>0</v>
       </c>
+      <c r="AH66">
+        <v>0</v>
+      </c>
+      <c r="AI66">
+        <v>0</v>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="1:33">
+    <row r="67" spans="1:36">
       <c r="A67">
         <v>65</v>
       </c>
@@ -9778,14 +10642,14 @@
       <c r="Y67">
         <v>22</v>
       </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
+      <c r="Z67" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>34</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -9802,8 +10666,17 @@
       <c r="AG67">
         <v>0</v>
       </c>
+      <c r="AH67">
+        <v>0</v>
+      </c>
+      <c r="AI67">
+        <v>0</v>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
     </row>
-    <row r="68" spans="1:33">
+    <row r="68" spans="1:36">
       <c r="A68">
         <v>66</v>
       </c>
@@ -9879,14 +10752,14 @@
       <c r="Y68">
         <v>22</v>
       </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>0</v>
+      <c r="Z68" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>702</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -9903,8 +10776,17 @@
       <c r="AG68">
         <v>0</v>
       </c>
+      <c r="AH68">
+        <v>0</v>
+      </c>
+      <c r="AI68">
+        <v>0</v>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="1:33" ht="37.5">
+    <row r="69" spans="1:36" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -9980,14 +10862,14 @@
       <c r="Y69">
         <v>22</v>
       </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
+      <c r="Z69" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>34</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -10004,8 +10886,17 @@
       <c r="AG69">
         <v>0</v>
       </c>
+      <c r="AH69">
+        <v>0</v>
+      </c>
+      <c r="AI69">
+        <v>0</v>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="1:33" ht="37.5">
+    <row r="70" spans="1:36" ht="37.5">
       <c r="A70">
         <v>68</v>
       </c>
@@ -10081,14 +10972,14 @@
       <c r="Y70">
         <v>22</v>
       </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>0</v>
+      <c r="Z70" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>34</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -10100,13 +10991,22 @@
         <v>0</v>
       </c>
       <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>0</v>
+      </c>
+      <c r="AH70">
+        <v>0</v>
+      </c>
+      <c r="AI70">
         <v>1</v>
       </c>
-      <c r="AG70">
+      <c r="AJ70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:33">
+    <row r="71" spans="1:36">
       <c r="A71">
         <v>69</v>
       </c>
@@ -10138,12 +11038,6 @@
       <c r="Y71">
         <v>0</v>
       </c>
-      <c r="Z71">
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <v>0</v>
-      </c>
       <c r="AB71">
         <v>0</v>
       </c>
@@ -10162,8 +11056,17 @@
       <c r="AG71">
         <v>0</v>
       </c>
+      <c r="AH71">
+        <v>0</v>
+      </c>
+      <c r="AI71">
+        <v>0</v>
+      </c>
+      <c r="AJ71">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="1:33" ht="37.5">
+    <row r="72" spans="1:36" ht="37.5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -10239,32 +11142,41 @@
       <c r="Y72">
         <v>22</v>
       </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>0</v>
+      <c r="Z72" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>702</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
         <v>1</v>
       </c>
-      <c r="AD72">
-        <v>0</v>
-      </c>
-      <c r="AE72">
-        <v>0</v>
-      </c>
-      <c r="AF72">
-        <v>0</v>
-      </c>
       <c r="AG72">
+        <v>0</v>
+      </c>
+      <c r="AH72">
+        <v>0</v>
+      </c>
+      <c r="AI72">
+        <v>0</v>
+      </c>
+      <c r="AJ72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:33">
+    <row r="73" spans="1:36">
       <c r="A73">
         <v>71</v>
       </c>
@@ -10340,14 +11252,14 @@
       <c r="Y73">
         <v>22</v>
       </c>
-      <c r="Z73">
-        <v>0</v>
-      </c>
-      <c r="AA73">
-        <v>0</v>
+      <c r="Z73" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>702</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -10364,8 +11276,17 @@
       <c r="AG73">
         <v>0</v>
       </c>
+      <c r="AH73">
+        <v>0</v>
+      </c>
+      <c r="AI73">
+        <v>0</v>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="1:33">
+    <row r="74" spans="1:36">
       <c r="A74">
         <v>72</v>
       </c>
@@ -10441,14 +11362,14 @@
       <c r="Y74">
         <v>22</v>
       </c>
-      <c r="Z74">
-        <v>0</v>
-      </c>
-      <c r="AA74">
-        <v>0</v>
+      <c r="Z74" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>702</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -10465,8 +11386,17 @@
       <c r="AG74">
         <v>0</v>
       </c>
+      <c r="AH74">
+        <v>0</v>
+      </c>
+      <c r="AI74">
+        <v>0</v>
+      </c>
+      <c r="AJ74">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="1:33">
+    <row r="75" spans="1:36">
       <c r="A75">
         <v>73</v>
       </c>
@@ -10542,14 +11472,14 @@
       <c r="Y75">
         <v>22</v>
       </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <v>0</v>
+      <c r="Z75" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>34</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -10566,8 +11496,17 @@
       <c r="AG75">
         <v>0</v>
       </c>
+      <c r="AH75">
+        <v>0</v>
+      </c>
+      <c r="AI75">
+        <v>0</v>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="1:33" ht="37.5">
+    <row r="76" spans="1:36" ht="37.5">
       <c r="A76">
         <v>74</v>
       </c>
@@ -10643,14 +11582,14 @@
       <c r="Y76">
         <v>22</v>
       </c>
-      <c r="Z76">
-        <v>0</v>
-      </c>
-      <c r="AA76">
-        <v>0</v>
+      <c r="Z76" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>34</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -10667,8 +11606,17 @@
       <c r="AG76">
         <v>0</v>
       </c>
+      <c r="AH76">
+        <v>0</v>
+      </c>
+      <c r="AI76">
+        <v>0</v>
+      </c>
+      <c r="AJ76">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="1:33">
+    <row r="77" spans="1:36">
       <c r="A77">
         <v>75</v>
       </c>
@@ -10744,14 +11692,14 @@
       <c r="Y77">
         <v>22</v>
       </c>
-      <c r="Z77">
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <v>0</v>
+      <c r="Z77" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>702</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -10768,8 +11716,17 @@
       <c r="AG77">
         <v>0</v>
       </c>
+      <c r="AH77">
+        <v>0</v>
+      </c>
+      <c r="AI77">
+        <v>0</v>
+      </c>
+      <c r="AJ77">
+        <v>0</v>
+      </c>
     </row>
-    <row r="78" spans="1:33" ht="37.5">
+    <row r="78" spans="1:36" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -10845,14 +11802,14 @@
       <c r="Y78">
         <v>22</v>
       </c>
-      <c r="Z78">
-        <v>0</v>
-      </c>
-      <c r="AA78">
-        <v>0</v>
+      <c r="Z78" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>702</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -10869,8 +11826,17 @@
       <c r="AG78">
         <v>0</v>
       </c>
+      <c r="AH78">
+        <v>0</v>
+      </c>
+      <c r="AI78">
+        <v>0</v>
+      </c>
+      <c r="AJ78">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="1:33">
+    <row r="79" spans="1:36">
       <c r="A79">
         <v>77</v>
       </c>
@@ -10946,14 +11912,14 @@
       <c r="Y79">
         <v>22</v>
       </c>
-      <c r="Z79">
-        <v>0</v>
-      </c>
-      <c r="AA79">
-        <v>0</v>
+      <c r="Z79" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>34</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -10970,8 +11936,17 @@
       <c r="AG79">
         <v>0</v>
       </c>
+      <c r="AH79">
+        <v>0</v>
+      </c>
+      <c r="AI79">
+        <v>0</v>
+      </c>
+      <c r="AJ79">
+        <v>0</v>
+      </c>
     </row>
-    <row r="80" spans="1:33">
+    <row r="80" spans="1:36">
       <c r="A80">
         <v>78</v>
       </c>
@@ -11047,14 +12022,14 @@
       <c r="Y80">
         <v>22</v>
       </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-      <c r="AA80">
-        <v>0</v>
+      <c r="Z80" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>702</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -11071,8 +12046,17 @@
       <c r="AG80">
         <v>0</v>
       </c>
+      <c r="AH80">
+        <v>0</v>
+      </c>
+      <c r="AI80">
+        <v>0</v>
+      </c>
+      <c r="AJ80">
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:33" ht="37.5">
+    <row r="81" spans="1:36" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -11148,14 +12132,14 @@
       <c r="Y81">
         <v>22</v>
       </c>
-      <c r="Z81">
-        <v>0</v>
-      </c>
-      <c r="AA81">
-        <v>0</v>
+      <c r="Z81" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>34</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -11172,8 +12156,17 @@
       <c r="AG81">
         <v>0</v>
       </c>
+      <c r="AH81">
+        <v>0</v>
+      </c>
+      <c r="AI81">
+        <v>0</v>
+      </c>
+      <c r="AJ81">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="1:33">
+    <row r="82" spans="1:36">
       <c r="A82">
         <v>80</v>
       </c>
@@ -11249,14 +12242,14 @@
       <c r="Y82">
         <v>22</v>
       </c>
-      <c r="Z82">
-        <v>0</v>
-      </c>
-      <c r="AA82">
-        <v>0</v>
+      <c r="Z82" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>702</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -11273,8 +12266,17 @@
       <c r="AG82">
         <v>0</v>
       </c>
+      <c r="AH82">
+        <v>0</v>
+      </c>
+      <c r="AI82">
+        <v>0</v>
+      </c>
+      <c r="AJ82">
+        <v>0</v>
+      </c>
     </row>
-    <row r="83" spans="1:33" ht="37.5">
+    <row r="83" spans="1:36" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -11350,14 +12352,14 @@
       <c r="Y83">
         <v>22</v>
       </c>
-      <c r="Z83">
-        <v>0</v>
-      </c>
-      <c r="AA83">
-        <v>0</v>
+      <c r="Z83" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>34</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -11374,8 +12376,17 @@
       <c r="AG83">
         <v>0</v>
       </c>
+      <c r="AH83">
+        <v>0</v>
+      </c>
+      <c r="AI83">
+        <v>0</v>
+      </c>
+      <c r="AJ83">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="1:33">
+    <row r="84" spans="1:36">
       <c r="A84">
         <v>82</v>
       </c>
@@ -11451,14 +12462,14 @@
       <c r="Y84">
         <v>22</v>
       </c>
-      <c r="Z84">
-        <v>0</v>
-      </c>
-      <c r="AA84">
-        <v>0</v>
+      <c r="Z84" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>702</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -11475,8 +12486,17 @@
       <c r="AG84">
         <v>0</v>
       </c>
+      <c r="AH84">
+        <v>0</v>
+      </c>
+      <c r="AI84">
+        <v>0</v>
+      </c>
+      <c r="AJ84">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="1:33">
+    <row r="85" spans="1:36">
       <c r="A85">
         <v>83</v>
       </c>
@@ -11552,14 +12572,14 @@
       <c r="Y85">
         <v>22</v>
       </c>
-      <c r="Z85">
-        <v>0</v>
-      </c>
-      <c r="AA85">
-        <v>0</v>
+      <c r="Z85" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>34</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -11576,8 +12596,17 @@
       <c r="AG85">
         <v>0</v>
       </c>
+      <c r="AH85">
+        <v>0</v>
+      </c>
+      <c r="AI85">
+        <v>0</v>
+      </c>
+      <c r="AJ85">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="1:33">
+    <row r="86" spans="1:36">
       <c r="A86">
         <v>84</v>
       </c>
@@ -11653,14 +12682,14 @@
       <c r="Y86">
         <v>22</v>
       </c>
-      <c r="Z86">
-        <v>0</v>
-      </c>
-      <c r="AA86">
-        <v>0</v>
+      <c r="Z86" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>702</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -11677,8 +12706,17 @@
       <c r="AG86">
         <v>0</v>
       </c>
+      <c r="AH86">
+        <v>0</v>
+      </c>
+      <c r="AI86">
+        <v>0</v>
+      </c>
+      <c r="AJ86">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="1:33">
+    <row r="87" spans="1:36" ht="37.5">
       <c r="A87">
         <v>85</v>
       </c>
@@ -11754,14 +12792,14 @@
       <c r="Y87">
         <v>22</v>
       </c>
-      <c r="Z87">
-        <v>0</v>
-      </c>
-      <c r="AA87">
-        <v>0</v>
+      <c r="Z87" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>34</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -11778,8 +12816,17 @@
       <c r="AG87">
         <v>0</v>
       </c>
+      <c r="AH87">
+        <v>0</v>
+      </c>
+      <c r="AI87">
+        <v>0</v>
+      </c>
+      <c r="AJ87">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="1:33">
+    <row r="88" spans="1:36">
       <c r="A88">
         <v>86</v>
       </c>
@@ -11855,32 +12902,41 @@
       <c r="Y88">
         <v>22</v>
       </c>
-      <c r="Z88">
-        <v>0</v>
-      </c>
-      <c r="AA88">
+      <c r="Z88" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB88">
+        <v>22</v>
+      </c>
+      <c r="AC88">
+        <v>0</v>
+      </c>
+      <c r="AD88">
         <v>2</v>
       </c>
-      <c r="AB88">
-        <v>0</v>
-      </c>
-      <c r="AC88">
+      <c r="AE88">
+        <v>0</v>
+      </c>
+      <c r="AF88">
         <v>1</v>
       </c>
-      <c r="AD88">
-        <v>0</v>
-      </c>
-      <c r="AE88">
-        <v>0</v>
-      </c>
-      <c r="AF88">
-        <v>0</v>
-      </c>
       <c r="AG88">
         <v>0</v>
       </c>
+      <c r="AH88">
+        <v>0</v>
+      </c>
+      <c r="AI88">
+        <v>0</v>
+      </c>
+      <c r="AJ88">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="1:33">
+    <row r="89" spans="1:36">
       <c r="A89">
         <v>87</v>
       </c>
@@ -11956,14 +13012,14 @@
       <c r="Y89">
         <v>22</v>
       </c>
-      <c r="Z89">
-        <v>0</v>
-      </c>
-      <c r="AA89">
-        <v>0</v>
+      <c r="Z89" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>34</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -11980,8 +13036,17 @@
       <c r="AG89">
         <v>0</v>
       </c>
+      <c r="AH89">
+        <v>0</v>
+      </c>
+      <c r="AI89">
+        <v>0</v>
+      </c>
+      <c r="AJ89">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="1:33">
+    <row r="90" spans="1:36">
       <c r="A90">
         <v>88</v>
       </c>
@@ -11989,15 +13054,6 @@
       <c r="I90" s="5"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="Z90">
-        <v>0</v>
-      </c>
-      <c r="AA90">
-        <v>0</v>
-      </c>
-      <c r="AB90">
-        <v>0</v>
-      </c>
       <c r="AC90">
         <v>0</v>
       </c>
@@ -12013,8 +13069,17 @@
       <c r="AG90">
         <v>0</v>
       </c>
+      <c r="AH90">
+        <v>0</v>
+      </c>
+      <c r="AI90">
+        <v>0</v>
+      </c>
+      <c r="AJ90">
+        <v>0</v>
+      </c>
     </row>
-    <row r="91" spans="1:33">
+    <row r="91" spans="1:36">
       <c r="A91">
         <v>89</v>
       </c>
@@ -12023,7 +13088,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="1:33">
+    <row r="92" spans="1:36">
       <c r="A92">
         <v>90</v>
       </c>
@@ -12032,7 +13097,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="1:33">
+    <row r="93" spans="1:36">
       <c r="A93">
         <v>91</v>
       </c>
@@ -12041,7 +13106,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="1:33">
+    <row r="94" spans="1:36">
       <c r="A94">
         <v>92</v>
       </c>
@@ -12050,7 +13115,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="1:33">
+    <row r="95" spans="1:36">
       <c r="A95">
         <v>93</v>
       </c>
@@ -12059,7 +13124,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="1:33">
+    <row r="96" spans="1:36">
       <c r="A96">
         <v>94</v>
       </c>

--- a/Assets/Originals/Excels/Talk/TalkMessage.xlsx
+++ b/Assets/Originals/Excels/Talk/TalkMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Talk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9A8526-432F-4158-A2D9-CCF5D90C32FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572A4392-7066-4471-88AE-F982E8F483C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="870">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -3003,6 +3003,279 @@
   </si>
   <si>
     <t>mais continuons à faire de notre mieux, IF.</t>
+  </si>
+  <si>
+    <t>messageTurkish</t>
+  </si>
+  <si>
+    <t>speakerNameTurkish</t>
+  </si>
+  <si>
+    <t>messageSizeTurkish</t>
+  </si>
+  <si>
+    <t>Burası… neresi…?</t>
+  </si>
+  <si>
+    <t>Sen</t>
+  </si>
+  <si>
+    <t>Görünüşe göre uyandın.</t>
+  </si>
+  <si>
+    <t>Benim adım Kaname.
+“Mumei”nin rehberiyim.</t>
+  </si>
+  <si>
+    <t>Burası, bu Ebedî Dünya'daki devasa labirentin adı.</t>
+  </si>
+  <si>
+    <t>Sen yaşayanlar dünyasında bir “günah” işledin ve öldün.
+Günah işleyen herkes burada, Mumei'de hapsedilir.</t>
+  </si>
+  <si>
+    <t>Yani sen de onlardan birisin.</t>
+  </si>
+  <si>
+    <t>Günah mı?</t>
+  </si>
+  <si>
+    <t>Evet. Çok ama çok büyük bir günah.</t>
+  </si>
+  <si>
+    <t>Bu arada, kendi adını hatırlıyor musun?</t>
+  </si>
+  <si>
+    <t>Şey… benim adım…</t>
+  </si>
+  <si>
+    <t>Ha…? Hatırlamıyorum…</t>
+  </si>
+  <si>
+    <t>Hatırlamaman çok doğal.</t>
+  </si>
+  <si>
+    <t>Çünkü bu labirente gelmeden önce adın yok edildi.</t>
+  </si>
+  <si>
+    <t>Adım… yok mu edildi…?</t>
+  </si>
+  <si>
+    <t>Bu ne demek?</t>
+  </si>
+  <si>
+    <t>Ebedî Dünya'da adı yok edilenler,
+kendi adlarını bir daha hatırlayamazlar.</t>
+  </si>
+  <si>
+    <t>Ne……</t>
+  </si>
+  <si>
+    <t>Ve adını hatırlayamayanlar…</t>
+  </si>
+  <si>
+    <t>…her türlü acıya katlanarak
+bu labirentte sonsuza dek dolaşacaklar.</t>
+  </si>
+  <si>
+    <t>Er ya da geç sen de öyle olacaksın.</t>
+  </si>
+  <si>
+    <t>Hayır… bu çok acımasızca…</t>
+  </si>
+  <si>
+    <t>Neden…</t>
+  </si>
+  <si>
+    <t>Çünkü günahkârların bir ada ihtiyacı yok.</t>
+  </si>
+  <si>
+    <t>Ama endişelenme.</t>
+  </si>
+  <si>
+    <t>Yaşayanlar dünyasında işlediğin günahı hatırlar
+ve bu labirentten kaçarsan, sana adını söylerim.</t>
+  </si>
+  <si>
+    <t>Böylece ne acı çekersin
+ne de dolaşıp durursun.</t>
+  </si>
+  <si>
+    <t>…Buradan kaçmak ister misin?</t>
+  </si>
+  <si>
+    <t>……Kaçmak istiyorum.</t>
+  </si>
+  <si>
+    <t>Ama nasıl kaçabilirim?</t>
+  </si>
+  <si>
+    <t>…Bir yolu var.</t>
+  </si>
+  <si>
+    <t>Benim sınavıma girip onu aşmak.</t>
+  </si>
+  <si>
+    <t>O zaman kaçabilirsin.</t>
+  </si>
+  <si>
+    <t>…Sınavıma girecek misin?</t>
+  </si>
+  <si>
+    <t>……Gireceğim.</t>
+  </si>
+  <si>
+    <t>…Anladım.
+O hâlde sınavın ne olduğunu anlatayım.</t>
+  </si>
+  <si>
+    <t>Sınavı geçmek için
+iki koşulu yerine getirmen gerekiyor.</t>
+  </si>
+  <si>
+    <t>Bir: Bu labirentten kaçmak.
+İki: Yaşayanlar dünyasında işlediğin günahı hatırlamak.</t>
+  </si>
+  <si>
+    <t>Bu labirentten nasıl kaçacağını anlatayım.</t>
+  </si>
+  <si>
+    <t>Kaçmak için, labirentin her köşesine saklanmış
+“Belgeler” ve “Gizemli Eşyalar”ı bulman gerekiyor.</t>
+  </si>
+  <si>
+    <t>Önce bir Belge edin.
+Dene bakalım, hemen önündeki çekmeceyi aç.</t>
+  </si>
+  <si>
+    <t>Az önce aldığın Belgenin içeriğine bir bak.</t>
+  </si>
+  <si>
+    <t>Sonra bir Gizemli Eşya edin.</t>
+  </si>
+  <si>
+    <t>Hemen önündeki iki çekmeceyi aç.</t>
+  </si>
+  <si>
+    <t>Az önce aldığın Gizemli Eşyalara bir bak.</t>
+  </si>
+  <si>
+    <t>Son olarak, içerideki “Yargının Mavi Küresi”ne dokun.</t>
+  </si>
+  <si>
+    <t>Belgenin içeriğiyle derin bağı olan
+Gizemli Eşyayı seçmelisin.</t>
+  </si>
+  <si>
+    <t>Sınavın açıklaması bu kadar.
+Bir sorun var mı?</t>
+  </si>
+  <si>
+    <t>Ha? İşlediğim günahı anlatmayacak mısın?</t>
+  </si>
+  <si>
+    <t>Anlatmayacağım.</t>
+  </si>
+  <si>
+    <t>“Ne”si yok.</t>
+  </si>
+  <si>
+    <t>Yaptığından gerçekten pişmansan,
+günahını hemen hatırlayabilmelisin.</t>
+  </si>
+  <si>
+    <t>Bu yüzden açıklama burada bitiyor.</t>
+  </si>
+  <si>
+    <t>Ayrıca adsız olmak zahmetli,
+o yüzden sana şimdilik “IF” diyeceğim.</t>
+  </si>
+  <si>
+    <t>Bu senin için uygun, değil mi?</t>
+  </si>
+  <si>
+    <t>Şey… e-evet……</t>
+  </si>
+  <si>
+    <t>Son olarak, bu labirentle ilgili önemli bir uyarı var.</t>
+  </si>
+  <si>
+    <t>Uyarı mı?</t>
+  </si>
+  <si>
+    <t>“Gezginler”e asla yakalanma.</t>
+  </si>
+  <si>
+    <t>Gezginler mi?</t>
+  </si>
+  <si>
+    <t>Mumei'de pusuya yatan canavarlar onlar.</t>
+  </si>
+  <si>
+    <t>IF, ne olursa olsun o canavarlara yakalanma.</t>
+  </si>
+  <si>
+    <t>Anladın mı?</t>
+  </si>
+  <si>
+    <t>……E-evet……</t>
+  </si>
+  <si>
+    <t>Pekâlâ, sınavı başlatalım.
+Arkandaki koridordan ilerle.</t>
+  </si>
+  <si>
+    <t>IF, sınavı geçmen için dua ediyorum.</t>
+  </si>
+  <si>
+    <t>…Sonunda… bu labirentten kaçabileceğim…</t>
+  </si>
+  <si>
+    <t>Ne… bu da ne……</t>
+  </si>
+  <si>
+    <t>Labirent neden hâlâ devam ediyor?!</t>
+  </si>
+  <si>
+    <t>Belli değil mi?</t>
+  </si>
+  <si>
+    <t>Çünkü labirentten henüz kaçamadın.</t>
+  </si>
+  <si>
+    <t>…Kaçamadım da ne demek?</t>
+  </si>
+  <si>
+    <t>Belgeleri de Gizemli Eşyaları da
+topladım ama!</t>
+  </si>
+  <si>
+    <t>Yoksa her şeyin bittiğini mi sandın?</t>
+  </si>
+  <si>
+    <t>Belgeler ve Gizemli Eşyalar
+başka bölgelerde de var.</t>
+  </si>
+  <si>
+    <t>Olamaz…</t>
+  </si>
+  <si>
+    <t>Üstelik IF, işlediğin günahı da hâlâ hatırlamadın, değil mi?</t>
+  </si>
+  <si>
+    <t>Bu yüzden sınav henüz bitmedi.</t>
+  </si>
+  <si>
+    <t>Hayır……</t>
+  </si>
+  <si>
+    <t>Mumei'nin asıl dehşeti şimdi başlıyor, IF.</t>
+  </si>
+  <si>
+    <t>Zor olacağını biliyorum,</t>
+  </si>
+  <si>
+    <t>ama elinden gelenin en iyisini yapmaya devam et, IF.</t>
   </si>
 </sst>
 </file>
@@ -3371,7 +3644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ102"/>
+  <dimension ref="A1:AM102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="123.375" style="2" customWidth="1"/>
@@ -3400,16 +3673,19 @@
     <col min="26" max="26" width="63.75" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="20.25" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="27.75" customWidth="1"/>
-    <col min="30" max="30" width="22.5" customWidth="1"/>
-    <col min="31" max="31" width="13.625" customWidth="1"/>
-    <col min="33" max="33" width="17.125" customWidth="1"/>
-    <col min="34" max="34" width="28.125" customWidth="1"/>
-    <col min="35" max="35" width="13.125" customWidth="1"/>
-    <col min="36" max="36" width="16" customWidth="1"/>
+    <col min="29" max="29" width="50.25" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="27.75" customWidth="1"/>
+    <col min="33" max="33" width="22.5" customWidth="1"/>
+    <col min="34" max="34" width="13.625" customWidth="1"/>
+    <col min="36" max="36" width="17.125" customWidth="1"/>
+    <col min="37" max="37" width="28.125" customWidth="1"/>
+    <col min="38" max="38" width="13.125" customWidth="1"/>
+    <col min="39" max="39" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:39">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3495,31 +3771,40 @@
         <v>700</v>
       </c>
       <c r="AC1" t="s">
+        <v>785</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>787</v>
+      </c>
+      <c r="AF1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH1" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AI1" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AJ1" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AK1" t="s">
         <v>26</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AL1" t="s">
         <v>27</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:39">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3554,12 +3839,6 @@
       <c r="AB2">
         <v>0</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
       <c r="AE2">
         <v>0</v>
       </c>
@@ -3578,8 +3857,17 @@
       <c r="AJ2">
         <v>0</v>
       </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:39">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3664,14 +3952,14 @@
       <c r="AB3">
         <v>22</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
+      <c r="AC3" t="s">
+        <v>788</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>789</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -3688,8 +3976,17 @@
       <c r="AJ3">
         <v>0</v>
       </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:39">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3774,32 +4071,41 @@
       <c r="AB4">
         <v>22</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" t="s">
+        <v>790</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AE4">
+        <v>22</v>
+      </c>
+      <c r="AF4">
         <v>1</v>
       </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
         <v>3</v>
       </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
       <c r="AJ4">
         <v>0</v>
       </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" ht="37.5">
+    <row r="5" spans="1:39" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3884,14 +4190,14 @@
       <c r="AB5">
         <v>22</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
+      <c r="AC5" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>34</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -3908,8 +4214,17 @@
       <c r="AJ5">
         <v>0</v>
       </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:39">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3994,14 +4309,14 @@
       <c r="AB6">
         <v>22</v>
       </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
+      <c r="AC6" t="s">
+        <v>438</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>789</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -4018,8 +4333,17 @@
       <c r="AJ6">
         <v>0</v>
       </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:39">
       <c r="A7">
         <v>5</v>
       </c>
@@ -4104,14 +4428,14 @@
       <c r="AB7">
         <v>22</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
+      <c r="AC7" t="s">
+        <v>792</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>34</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -4128,8 +4452,17 @@
       <c r="AJ7">
         <v>0</v>
       </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" ht="75">
+    <row r="8" spans="1:39" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4214,14 +4547,14 @@
       <c r="AB8">
         <v>22</v>
       </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
+      <c r="AC8" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>34</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -4238,8 +4571,17 @@
       <c r="AJ8">
         <v>0</v>
       </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:39">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4324,14 +4666,14 @@
       <c r="AB9">
         <v>22</v>
       </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
+      <c r="AC9" t="s">
+        <v>794</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>34</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -4348,8 +4690,17 @@
       <c r="AJ9">
         <v>0</v>
       </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:39">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4434,14 +4785,14 @@
       <c r="AB10">
         <v>22</v>
       </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
+      <c r="AC10" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>789</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -4458,8 +4809,17 @@
       <c r="AJ10">
         <v>0</v>
       </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:39">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4544,14 +4904,14 @@
       <c r="AB11">
         <v>22</v>
       </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
+      <c r="AC11" t="s">
+        <v>796</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>34</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -4568,8 +4928,17 @@
       <c r="AJ11">
         <v>0</v>
       </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:39">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4654,14 +5023,14 @@
       <c r="AB12">
         <v>22</v>
       </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
+      <c r="AC12" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>34</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -4678,8 +5047,17 @@
       <c r="AJ12">
         <v>0</v>
       </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:39">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4764,21 +5142,21 @@
       <c r="AB13">
         <v>22</v>
       </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
+      <c r="AC13" t="s">
+        <v>798</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>789</v>
+      </c>
+      <c r="AE13">
+        <v>22</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
         <v>1</v>
       </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
       <c r="AH13">
         <v>0</v>
       </c>
@@ -4788,8 +5166,17 @@
       <c r="AJ13">
         <v>0</v>
       </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:39">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4874,14 +5261,14 @@
       <c r="AB14">
         <v>22</v>
       </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
+      <c r="AC14" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>789</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -4898,8 +5285,17 @@
       <c r="AJ14">
         <v>0</v>
       </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:39">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4984,14 +5380,14 @@
       <c r="AB15">
         <v>22</v>
       </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
+      <c r="AC15" t="s">
+        <v>800</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>34</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF15">
         <v>0</v>
@@ -5008,8 +5404,17 @@
       <c r="AJ15">
         <v>0</v>
       </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" ht="37.5">
+    <row r="16" spans="1:39" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5094,14 +5499,14 @@
       <c r="AB16">
         <v>22</v>
       </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
+      <c r="AC16" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>34</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF16">
         <v>0</v>
@@ -5118,8 +5523,17 @@
       <c r="AJ16">
         <v>0</v>
       </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:39">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5204,14 +5618,14 @@
       <c r="AB17">
         <v>22</v>
       </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
+      <c r="AC17" t="s">
+        <v>802</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>789</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -5228,8 +5642,17 @@
       <c r="AJ17">
         <v>0</v>
       </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:36">
+    <row r="18" spans="1:39">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5314,14 +5737,14 @@
       <c r="AB18">
         <v>22</v>
       </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
+      <c r="AC18" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>789</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -5338,8 +5761,17 @@
       <c r="AJ18">
         <v>0</v>
       </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:36" ht="56.25">
+    <row r="19" spans="1:39" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5424,14 +5856,14 @@
       <c r="AB19">
         <v>22</v>
       </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
+      <c r="AC19" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>34</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -5448,8 +5880,17 @@
       <c r="AJ19">
         <v>0</v>
       </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:36">
+    <row r="20" spans="1:39">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5534,14 +5975,14 @@
       <c r="AB20">
         <v>22</v>
       </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
+      <c r="AC20" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>789</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF20">
         <v>0</v>
@@ -5558,8 +5999,17 @@
       <c r="AJ20">
         <v>0</v>
       </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:36">
+    <row r="21" spans="1:39">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5641,21 +6091,21 @@
       <c r="AB21">
         <v>22</v>
       </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
+      <c r="AC21" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE21">
+        <v>22</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
         <v>1</v>
       </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
       <c r="AH21">
         <v>0</v>
       </c>
@@ -5665,8 +6115,17 @@
       <c r="AJ21">
         <v>0</v>
       </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:36" ht="37.5">
+    <row r="22" spans="1:39" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5751,14 +6210,14 @@
       <c r="AB22">
         <v>22</v>
       </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
+      <c r="AC22" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>34</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -5775,8 +6234,17 @@
       <c r="AJ22">
         <v>0</v>
       </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:36" ht="37.5">
+    <row r="23" spans="1:39" ht="37.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5861,14 +6329,14 @@
       <c r="AB23">
         <v>22</v>
       </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
+      <c r="AC23" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>34</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF23">
         <v>0</v>
@@ -5885,8 +6353,17 @@
       <c r="AJ23">
         <v>0</v>
       </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:36">
+    <row r="24" spans="1:39">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5971,14 +6448,14 @@
       <c r="AB24">
         <v>22</v>
       </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
+      <c r="AC24" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>789</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF24">
         <v>0</v>
@@ -5995,8 +6472,17 @@
       <c r="AJ24">
         <v>0</v>
       </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:36">
+    <row r="25" spans="1:39">
       <c r="A25">
         <v>23</v>
       </c>
@@ -6081,14 +6567,14 @@
       <c r="AB25">
         <v>22</v>
       </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
+      <c r="AC25" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>789</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF25">
         <v>0</v>
@@ -6105,8 +6591,17 @@
       <c r="AJ25">
         <v>0</v>
       </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:36">
+    <row r="26" spans="1:39">
       <c r="A26">
         <v>24</v>
       </c>
@@ -6191,14 +6686,14 @@
       <c r="AB26">
         <v>22</v>
       </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
+      <c r="AC26" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>34</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF26">
         <v>0</v>
@@ -6215,8 +6710,17 @@
       <c r="AJ26">
         <v>0</v>
       </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:36">
+    <row r="27" spans="1:39">
       <c r="A27">
         <v>25</v>
       </c>
@@ -6301,14 +6805,14 @@
       <c r="AB27">
         <v>22</v>
       </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
+      <c r="AC27" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>34</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -6325,8 +6829,17 @@
       <c r="AJ27">
         <v>0</v>
       </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:36" ht="75">
+    <row r="28" spans="1:39" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -6411,14 +6924,14 @@
       <c r="AB28">
         <v>22</v>
       </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
+      <c r="AC28" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>34</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF28">
         <v>0</v>
@@ -6435,8 +6948,17 @@
       <c r="AJ28">
         <v>0</v>
       </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:36" ht="37.5">
+    <row r="29" spans="1:39" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -6521,32 +7043,41 @@
       <c r="AB29">
         <v>22</v>
       </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
+      <c r="AC29" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>34</v>
       </c>
       <c r="AE29">
+        <v>22</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
         <v>1</v>
       </c>
-      <c r="AF29">
+      <c r="AI29">
         <v>1</v>
       </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AI29">
-        <v>0</v>
-      </c>
       <c r="AJ29">
         <v>0</v>
       </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:36">
+    <row r="30" spans="1:39">
       <c r="A30">
         <v>28</v>
       </c>
@@ -6631,14 +7162,14 @@
       <c r="AB30">
         <v>22</v>
       </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
+      <c r="AC30" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>34</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -6655,8 +7186,17 @@
       <c r="AJ30">
         <v>0</v>
       </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:36">
+    <row r="31" spans="1:39">
       <c r="A31">
         <v>29</v>
       </c>
@@ -6741,14 +7281,14 @@
       <c r="AB31">
         <v>22</v>
       </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
+      <c r="AC31" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>789</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -6765,8 +7305,17 @@
       <c r="AJ31">
         <v>0</v>
       </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:36">
+    <row r="32" spans="1:39">
       <c r="A32">
         <v>30</v>
       </c>
@@ -6851,14 +7400,14 @@
       <c r="AB32">
         <v>22</v>
       </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
+      <c r="AC32" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>789</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -6875,8 +7424,17 @@
       <c r="AJ32">
         <v>0</v>
       </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:36">
+    <row r="33" spans="1:39">
       <c r="A33">
         <v>31</v>
       </c>
@@ -6961,14 +7519,14 @@
       <c r="AB33">
         <v>22</v>
       </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
+      <c r="AC33" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>34</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -6985,8 +7543,17 @@
       <c r="AJ33">
         <v>0</v>
       </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:36" ht="37.5">
+    <row r="34" spans="1:39" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -7071,14 +7638,14 @@
       <c r="AB34">
         <v>22</v>
       </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
+      <c r="AC34" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>34</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF34">
         <v>0</v>
@@ -7095,8 +7662,17 @@
       <c r="AJ34">
         <v>0</v>
       </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:36">
+    <row r="35" spans="1:39">
       <c r="A35">
         <v>33</v>
       </c>
@@ -7181,32 +7757,41 @@
       <c r="AB35">
         <v>22</v>
       </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
+      <c r="AC35" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>34</v>
       </c>
       <c r="AE35">
+        <v>22</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
         <v>1</v>
       </c>
-      <c r="AF35">
+      <c r="AI35">
         <v>1</v>
       </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35">
-        <v>0</v>
-      </c>
-      <c r="AI35">
-        <v>0</v>
-      </c>
       <c r="AJ35">
         <v>0</v>
       </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:36">
+    <row r="36" spans="1:39">
       <c r="A36">
         <v>34</v>
       </c>
@@ -7291,14 +7876,14 @@
       <c r="AB36">
         <v>22</v>
       </c>
-      <c r="AC36">
-        <v>0</v>
-      </c>
-      <c r="AD36">
-        <v>0</v>
+      <c r="AC36" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>34</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -7315,8 +7900,17 @@
       <c r="AJ36">
         <v>0</v>
       </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:36">
+    <row r="37" spans="1:39">
       <c r="A37">
         <v>35</v>
       </c>
@@ -7401,14 +7995,14 @@
       <c r="AB37">
         <v>22</v>
       </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
-      <c r="AD37">
-        <v>0</v>
+      <c r="AC37" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>789</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -7425,8 +8019,17 @@
       <c r="AJ37">
         <v>0</v>
       </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:36" ht="37.5">
+    <row r="38" spans="1:39" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -7511,32 +8114,41 @@
       <c r="AB38">
         <v>22</v>
       </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
-      <c r="AD38">
-        <v>0</v>
+      <c r="AC38" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>34</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF38">
         <v>0</v>
       </c>
       <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
         <v>1</v>
       </c>
-      <c r="AH38">
+      <c r="AK38">
         <v>9</v>
       </c>
-      <c r="AI38">
-        <v>0</v>
-      </c>
-      <c r="AJ38">
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:36">
+    <row r="39" spans="1:39">
       <c r="A39">
         <v>37</v>
       </c>
@@ -7571,12 +8183,6 @@
       <c r="AB39">
         <v>0</v>
       </c>
-      <c r="AC39">
-        <v>0</v>
-      </c>
-      <c r="AD39">
-        <v>0</v>
-      </c>
       <c r="AE39">
         <v>0</v>
       </c>
@@ -7595,8 +8201,17 @@
       <c r="AJ39">
         <v>0</v>
       </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:36" ht="37.5">
+    <row r="40" spans="1:39" ht="37.5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -7681,14 +8296,14 @@
       <c r="AB40">
         <v>22</v>
       </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
+      <c r="AC40" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>34</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF40">
         <v>0</v>
@@ -7705,8 +8320,17 @@
       <c r="AJ40">
         <v>0</v>
       </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:36" ht="85.5" customHeight="1">
+    <row r="41" spans="1:39" ht="85.5" customHeight="1">
       <c r="A41">
         <v>39</v>
       </c>
@@ -7791,14 +8415,14 @@
       <c r="AB41">
         <v>22</v>
       </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
+      <c r="AC41" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>34</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF41">
         <v>0</v>
@@ -7815,8 +8439,17 @@
       <c r="AJ41">
         <v>0</v>
       </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:36" ht="51.75" customHeight="1">
+    <row r="42" spans="1:39" ht="51.75" customHeight="1">
       <c r="A42">
         <v>40</v>
       </c>
@@ -7901,14 +8534,14 @@
       <c r="AB42">
         <v>22</v>
       </c>
-      <c r="AC42">
-        <v>0</v>
-      </c>
-      <c r="AD42">
-        <v>0</v>
+      <c r="AC42" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>34</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF42">
         <v>0</v>
@@ -7925,8 +8558,17 @@
       <c r="AJ42">
         <v>0</v>
       </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:36" ht="56.25">
+    <row r="43" spans="1:39" ht="56.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -8011,14 +8653,14 @@
       <c r="AB43">
         <v>22</v>
       </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
+      <c r="AC43" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>34</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -8035,8 +8677,17 @@
       <c r="AJ43">
         <v>0</v>
       </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:36" ht="37.5">
+    <row r="44" spans="1:39" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -8121,32 +8772,41 @@
       <c r="AB44">
         <v>22</v>
       </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
-      <c r="AD44">
-        <v>0</v>
+      <c r="AC44" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>34</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF44">
         <v>0</v>
       </c>
       <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AI44">
+        <v>0</v>
+      </c>
+      <c r="AJ44">
         <v>2</v>
       </c>
-      <c r="AH44">
+      <c r="AK44">
         <v>10</v>
       </c>
-      <c r="AI44">
-        <v>0</v>
-      </c>
-      <c r="AJ44">
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="56.25">
+    <row r="45" spans="1:39" ht="56.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -8231,32 +8891,41 @@
       <c r="AB45">
         <v>22</v>
       </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AD45">
-        <v>0</v>
+      <c r="AC45" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>34</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF45">
         <v>0</v>
       </c>
       <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
         <v>2</v>
       </c>
-      <c r="AH45">
+      <c r="AK45">
         <v>11</v>
       </c>
-      <c r="AI45">
-        <v>0</v>
-      </c>
-      <c r="AJ45">
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="37.5">
+    <row r="46" spans="1:39" ht="37.5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -8341,14 +9010,14 @@
       <c r="AB46">
         <v>22</v>
       </c>
-      <c r="AC46">
-        <v>0</v>
-      </c>
-      <c r="AD46">
-        <v>0</v>
+      <c r="AC46" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>34</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF46">
         <v>0</v>
@@ -8365,8 +9034,17 @@
       <c r="AJ46">
         <v>0</v>
       </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:36">
+    <row r="47" spans="1:39">
       <c r="A47">
         <v>45</v>
       </c>
@@ -8451,32 +9129,41 @@
       <c r="AB47">
         <v>22</v>
       </c>
-      <c r="AC47">
-        <v>0</v>
-      </c>
-      <c r="AD47">
-        <v>0</v>
+      <c r="AC47" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>34</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF47">
         <v>0</v>
       </c>
       <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47">
+        <v>0</v>
+      </c>
+      <c r="AI47">
+        <v>0</v>
+      </c>
+      <c r="AJ47">
         <v>3</v>
       </c>
-      <c r="AH47">
+      <c r="AK47">
         <v>12</v>
       </c>
-      <c r="AI47">
-        <v>0</v>
-      </c>
-      <c r="AJ47">
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="37.5">
+    <row r="48" spans="1:39" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -8561,32 +9248,41 @@
       <c r="AB48">
         <v>22</v>
       </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
+      <c r="AC48" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>34</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF48">
         <v>0</v>
       </c>
       <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48">
+        <v>0</v>
+      </c>
+      <c r="AI48">
+        <v>0</v>
+      </c>
+      <c r="AJ48">
         <v>2</v>
       </c>
-      <c r="AH48">
+      <c r="AK48">
         <v>13</v>
       </c>
-      <c r="AI48">
-        <v>0</v>
-      </c>
-      <c r="AJ48">
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="37.5">
+    <row r="49" spans="1:39" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -8671,14 +9367,14 @@
       <c r="AB49">
         <v>22</v>
       </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
+      <c r="AC49" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>34</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF49">
         <v>0</v>
@@ -8695,8 +9391,17 @@
       <c r="AJ49">
         <v>0</v>
       </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:36" ht="56.25">
+    <row r="50" spans="1:39" ht="56.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -8781,32 +9486,41 @@
       <c r="AB50">
         <v>22</v>
       </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
+      <c r="AC50" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>34</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF50">
         <v>0</v>
       </c>
       <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50">
+        <v>0</v>
+      </c>
+      <c r="AI50">
+        <v>0</v>
+      </c>
+      <c r="AJ50">
         <v>2</v>
       </c>
-      <c r="AH50">
+      <c r="AK50">
         <v>14</v>
       </c>
-      <c r="AI50">
-        <v>0</v>
-      </c>
-      <c r="AJ50">
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="37.5">
+    <row r="51" spans="1:39" ht="37.5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -8891,14 +9605,14 @@
       <c r="AB51">
         <v>22</v>
       </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
+      <c r="AC51" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>34</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF51">
         <v>0</v>
@@ -8915,8 +9629,17 @@
       <c r="AJ51">
         <v>0</v>
       </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:36" ht="37.5">
+    <row r="52" spans="1:39" ht="37.5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -9001,14 +9724,14 @@
       <c r="AB52">
         <v>22</v>
       </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
-      <c r="AD52">
-        <v>0</v>
+      <c r="AC52" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>789</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF52">
         <v>0</v>
@@ -9025,8 +9748,17 @@
       <c r="AJ52">
         <v>0</v>
       </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:39">
       <c r="A53">
         <v>51</v>
       </c>
@@ -9111,14 +9843,14 @@
       <c r="AB53">
         <v>22</v>
       </c>
-      <c r="AC53">
-        <v>0</v>
-      </c>
-      <c r="AD53">
-        <v>0</v>
+      <c r="AC53" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>34</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -9135,8 +9867,17 @@
       <c r="AJ53">
         <v>0</v>
       </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:39">
       <c r="A54">
         <v>52</v>
       </c>
@@ -9221,14 +9962,14 @@
       <c r="AB54">
         <v>22</v>
       </c>
-      <c r="AC54">
-        <v>0</v>
-      </c>
-      <c r="AD54">
-        <v>0</v>
+      <c r="AC54" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>789</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF54">
         <v>0</v>
@@ -9245,8 +9986,17 @@
       <c r="AJ54">
         <v>0</v>
       </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:39">
       <c r="A55">
         <v>53</v>
       </c>
@@ -9331,14 +10081,14 @@
       <c r="AB55">
         <v>22</v>
       </c>
-      <c r="AC55">
-        <v>0</v>
-      </c>
-      <c r="AD55">
-        <v>0</v>
+      <c r="AC55" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>34</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF55">
         <v>0</v>
@@ -9355,8 +10105,17 @@
       <c r="AJ55">
         <v>0</v>
       </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:36" ht="56.25">
+    <row r="56" spans="1:39" ht="56.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -9441,14 +10200,14 @@
       <c r="AB56">
         <v>22</v>
       </c>
-      <c r="AC56">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>0</v>
+      <c r="AC56" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>34</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF56">
         <v>0</v>
@@ -9465,8 +10224,17 @@
       <c r="AJ56">
         <v>0</v>
       </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:39">
       <c r="A57">
         <v>55</v>
       </c>
@@ -9551,14 +10319,14 @@
       <c r="AB57">
         <v>22</v>
       </c>
-      <c r="AC57">
-        <v>0</v>
-      </c>
-      <c r="AD57">
-        <v>0</v>
+      <c r="AC57" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>34</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF57">
         <v>0</v>
@@ -9575,8 +10343,17 @@
       <c r="AJ57">
         <v>0</v>
       </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:36" ht="37.5">
+    <row r="58" spans="1:39" ht="37.5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -9661,14 +10438,14 @@
       <c r="AB58">
         <v>22</v>
       </c>
-      <c r="AC58">
-        <v>0</v>
-      </c>
-      <c r="AD58">
-        <v>0</v>
+      <c r="AC58" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>34</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF58">
         <v>0</v>
@@ -9685,8 +10462,17 @@
       <c r="AJ58">
         <v>0</v>
       </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="1:36">
+    <row r="59" spans="1:39">
       <c r="A59">
         <v>57</v>
       </c>
@@ -9771,14 +10557,14 @@
       <c r="AB59">
         <v>22</v>
       </c>
-      <c r="AC59">
-        <v>0</v>
-      </c>
-      <c r="AD59">
-        <v>0</v>
+      <c r="AC59" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>34</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF59">
         <v>0</v>
@@ -9795,8 +10581,17 @@
       <c r="AJ59">
         <v>0</v>
       </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="1:36">
+    <row r="60" spans="1:39">
       <c r="A60">
         <v>58</v>
       </c>
@@ -9881,14 +10676,14 @@
       <c r="AB60">
         <v>22</v>
       </c>
-      <c r="AC60">
-        <v>0</v>
-      </c>
-      <c r="AD60">
-        <v>0</v>
+      <c r="AC60" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>789</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF60">
         <v>0</v>
@@ -9905,8 +10700,17 @@
       <c r="AJ60">
         <v>0</v>
       </c>
+      <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="1:36" ht="37.5">
+    <row r="61" spans="1:39" ht="37.5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -9991,14 +10795,14 @@
       <c r="AB61">
         <v>22</v>
       </c>
-      <c r="AC61">
-        <v>0</v>
-      </c>
-      <c r="AD61">
-        <v>0</v>
+      <c r="AC61" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>34</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF61">
         <v>0</v>
@@ -10015,8 +10819,17 @@
       <c r="AJ61">
         <v>0</v>
       </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="1:36">
+    <row r="62" spans="1:39">
       <c r="A62">
         <v>60</v>
       </c>
@@ -10101,21 +10914,21 @@
       <c r="AB62">
         <v>22</v>
       </c>
-      <c r="AC62">
-        <v>0</v>
-      </c>
-      <c r="AD62">
+      <c r="AC62" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>789</v>
+      </c>
+      <c r="AE62">
+        <v>22</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
         <v>1</v>
       </c>
-      <c r="AE62">
-        <v>0</v>
-      </c>
-      <c r="AF62">
-        <v>0</v>
-      </c>
-      <c r="AG62">
-        <v>0</v>
-      </c>
       <c r="AH62">
         <v>0</v>
       </c>
@@ -10125,8 +10938,17 @@
       <c r="AJ62">
         <v>0</v>
       </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="1:36">
+    <row r="63" spans="1:39">
       <c r="A63">
         <v>61</v>
       </c>
@@ -10211,14 +11033,14 @@
       <c r="AB63">
         <v>22</v>
       </c>
-      <c r="AC63">
-        <v>0</v>
-      </c>
-      <c r="AD63">
-        <v>0</v>
+      <c r="AC63" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>34</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF63">
         <v>0</v>
@@ -10235,8 +11057,17 @@
       <c r="AJ63">
         <v>0</v>
       </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="1:36">
+    <row r="64" spans="1:39">
       <c r="A64">
         <v>62</v>
       </c>
@@ -10321,14 +11152,14 @@
       <c r="AB64">
         <v>22</v>
       </c>
-      <c r="AC64">
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <v>0</v>
+      <c r="AC64" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>789</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF64">
         <v>0</v>
@@ -10345,8 +11176,17 @@
       <c r="AJ64">
         <v>0</v>
       </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="1:36">
+    <row r="65" spans="1:39">
       <c r="A65">
         <v>63</v>
       </c>
@@ -10431,14 +11271,14 @@
       <c r="AB65">
         <v>22</v>
       </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
+      <c r="AC65" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>34</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF65">
         <v>0</v>
@@ -10455,8 +11295,17 @@
       <c r="AJ65">
         <v>0</v>
       </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:36" ht="37.5">
+    <row r="66" spans="1:39" ht="37.5">
       <c r="A66">
         <v>64</v>
       </c>
@@ -10541,14 +11390,14 @@
       <c r="AB66">
         <v>22</v>
       </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
+      <c r="AC66" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>34</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF66">
         <v>0</v>
@@ -10565,8 +11414,17 @@
       <c r="AJ66">
         <v>0</v>
       </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="1:36">
+    <row r="67" spans="1:39">
       <c r="A67">
         <v>65</v>
       </c>
@@ -10651,14 +11509,14 @@
       <c r="AB67">
         <v>22</v>
       </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
+      <c r="AC67" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>34</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF67">
         <v>0</v>
@@ -10675,8 +11533,17 @@
       <c r="AJ67">
         <v>0</v>
       </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>0</v>
+      </c>
     </row>
-    <row r="68" spans="1:36">
+    <row r="68" spans="1:39">
       <c r="A68">
         <v>66</v>
       </c>
@@ -10761,14 +11628,14 @@
       <c r="AB68">
         <v>22</v>
       </c>
-      <c r="AC68">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>0</v>
+      <c r="AC68" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>789</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF68">
         <v>0</v>
@@ -10785,8 +11652,17 @@
       <c r="AJ68">
         <v>0</v>
       </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="1:36" ht="37.5">
+    <row r="69" spans="1:39" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
@@ -10871,14 +11747,14 @@
       <c r="AB69">
         <v>22</v>
       </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>0</v>
+      <c r="AC69" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>34</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF69">
         <v>0</v>
@@ -10895,8 +11771,17 @@
       <c r="AJ69">
         <v>0</v>
       </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="1:36" ht="37.5">
+    <row r="70" spans="1:39" ht="37.5">
       <c r="A70">
         <v>68</v>
       </c>
@@ -10981,14 +11866,14 @@
       <c r="AB70">
         <v>22</v>
       </c>
-      <c r="AC70">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
+      <c r="AC70" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>34</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF70">
         <v>0</v>
@@ -11000,13 +11885,22 @@
         <v>0</v>
       </c>
       <c r="AI70">
+        <v>0</v>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
         <v>1</v>
       </c>
-      <c r="AJ70">
+      <c r="AM70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:36">
+    <row r="71" spans="1:39">
       <c r="A71">
         <v>69</v>
       </c>
@@ -11041,12 +11935,6 @@
       <c r="AB71">
         <v>0</v>
       </c>
-      <c r="AC71">
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <v>0</v>
-      </c>
       <c r="AE71">
         <v>0</v>
       </c>
@@ -11065,8 +11953,17 @@
       <c r="AJ71">
         <v>0</v>
       </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="1:36" ht="37.5">
+    <row r="72" spans="1:39" ht="37.5">
       <c r="A72">
         <v>70</v>
       </c>
@@ -11151,32 +12048,41 @@
       <c r="AB72">
         <v>22</v>
       </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>0</v>
+      <c r="AC72" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>789</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
+        <v>0</v>
+      </c>
+      <c r="AH72">
+        <v>0</v>
+      </c>
+      <c r="AI72">
         <v>1</v>
       </c>
-      <c r="AG72">
-        <v>0</v>
-      </c>
-      <c r="AH72">
-        <v>0</v>
-      </c>
-      <c r="AI72">
-        <v>0</v>
-      </c>
       <c r="AJ72">
+        <v>0</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:36">
+    <row r="73" spans="1:39">
       <c r="A73">
         <v>71</v>
       </c>
@@ -11261,14 +12167,14 @@
       <c r="AB73">
         <v>22</v>
       </c>
-      <c r="AC73">
-        <v>0</v>
-      </c>
-      <c r="AD73">
-        <v>0</v>
+      <c r="AC73" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>789</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF73">
         <v>0</v>
@@ -11285,8 +12191,17 @@
       <c r="AJ73">
         <v>0</v>
       </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="1:36">
+    <row r="74" spans="1:39">
       <c r="A74">
         <v>72</v>
       </c>
@@ -11371,14 +12286,14 @@
       <c r="AB74">
         <v>22</v>
       </c>
-      <c r="AC74">
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <v>0</v>
+      <c r="AC74" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>789</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF74">
         <v>0</v>
@@ -11395,8 +12310,17 @@
       <c r="AJ74">
         <v>0</v>
       </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="1:36">
+    <row r="75" spans="1:39">
       <c r="A75">
         <v>73</v>
       </c>
@@ -11481,14 +12405,14 @@
       <c r="AB75">
         <v>22</v>
       </c>
-      <c r="AC75">
-        <v>0</v>
-      </c>
-      <c r="AD75">
-        <v>0</v>
+      <c r="AC75" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>34</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF75">
         <v>0</v>
@@ -11505,8 +12429,17 @@
       <c r="AJ75">
         <v>0</v>
       </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="1:36" ht="37.5">
+    <row r="76" spans="1:39">
       <c r="A76">
         <v>74</v>
       </c>
@@ -11591,14 +12524,14 @@
       <c r="AB76">
         <v>22</v>
       </c>
-      <c r="AC76">
-        <v>0</v>
-      </c>
-      <c r="AD76">
-        <v>0</v>
+      <c r="AC76" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>34</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF76">
         <v>0</v>
@@ -11615,8 +12548,17 @@
       <c r="AJ76">
         <v>0</v>
       </c>
+      <c r="AK76">
+        <v>0</v>
+      </c>
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="1:36">
+    <row r="77" spans="1:39">
       <c r="A77">
         <v>75</v>
       </c>
@@ -11701,14 +12643,14 @@
       <c r="AB77">
         <v>22</v>
       </c>
-      <c r="AC77">
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <v>0</v>
+      <c r="AC77" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>789</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF77">
         <v>0</v>
@@ -11725,8 +12667,17 @@
       <c r="AJ77">
         <v>0</v>
       </c>
+      <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
+        <v>0</v>
+      </c>
+      <c r="AM77">
+        <v>0</v>
+      </c>
     </row>
-    <row r="78" spans="1:36" ht="37.5">
+    <row r="78" spans="1:39" ht="37.5">
       <c r="A78">
         <v>76</v>
       </c>
@@ -11811,14 +12762,14 @@
       <c r="AB78">
         <v>22</v>
       </c>
-      <c r="AC78">
-        <v>0</v>
-      </c>
-      <c r="AD78">
-        <v>0</v>
+      <c r="AC78" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>789</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF78">
         <v>0</v>
@@ -11835,8 +12786,17 @@
       <c r="AJ78">
         <v>0</v>
       </c>
+      <c r="AK78">
+        <v>0</v>
+      </c>
+      <c r="AL78">
+        <v>0</v>
+      </c>
+      <c r="AM78">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="1:36">
+    <row r="79" spans="1:39">
       <c r="A79">
         <v>77</v>
       </c>
@@ -11921,14 +12881,14 @@
       <c r="AB79">
         <v>22</v>
       </c>
-      <c r="AC79">
-        <v>0</v>
-      </c>
-      <c r="AD79">
-        <v>0</v>
+      <c r="AC79" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>34</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF79">
         <v>0</v>
@@ -11945,8 +12905,17 @@
       <c r="AJ79">
         <v>0</v>
       </c>
+      <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>0</v>
+      </c>
     </row>
-    <row r="80" spans="1:36">
+    <row r="80" spans="1:39">
       <c r="A80">
         <v>78</v>
       </c>
@@ -12031,14 +13000,14 @@
       <c r="AB80">
         <v>22</v>
       </c>
-      <c r="AC80">
-        <v>0</v>
-      </c>
-      <c r="AD80">
-        <v>0</v>
+      <c r="AC80" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>789</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF80">
         <v>0</v>
@@ -12055,8 +13024,17 @@
       <c r="AJ80">
         <v>0</v>
       </c>
+      <c r="AK80">
+        <v>0</v>
+      </c>
+      <c r="AL80">
+        <v>0</v>
+      </c>
+      <c r="AM80">
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:36" ht="37.5">
+    <row r="81" spans="1:39" ht="37.5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -12141,14 +13119,14 @@
       <c r="AB81">
         <v>22</v>
       </c>
-      <c r="AC81">
-        <v>0</v>
-      </c>
-      <c r="AD81">
-        <v>0</v>
+      <c r="AC81" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>34</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF81">
         <v>0</v>
@@ -12165,8 +13143,17 @@
       <c r="AJ81">
         <v>0</v>
       </c>
+      <c r="AK81">
+        <v>0</v>
+      </c>
+      <c r="AL81">
+        <v>0</v>
+      </c>
+      <c r="AM81">
+        <v>0</v>
+      </c>
     </row>
-    <row r="82" spans="1:36">
+    <row r="82" spans="1:39">
       <c r="A82">
         <v>80</v>
       </c>
@@ -12251,14 +13238,14 @@
       <c r="AB82">
         <v>22</v>
       </c>
-      <c r="AC82">
-        <v>0</v>
-      </c>
-      <c r="AD82">
-        <v>0</v>
+      <c r="AC82" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>789</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF82">
         <v>0</v>
@@ -12275,8 +13262,17 @@
       <c r="AJ82">
         <v>0</v>
       </c>
+      <c r="AK82">
+        <v>0</v>
+      </c>
+      <c r="AL82">
+        <v>0</v>
+      </c>
+      <c r="AM82">
+        <v>0</v>
+      </c>
     </row>
-    <row r="83" spans="1:36" ht="37.5">
+    <row r="83" spans="1:39" ht="37.5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -12361,14 +13357,14 @@
       <c r="AB83">
         <v>22</v>
       </c>
-      <c r="AC83">
-        <v>0</v>
-      </c>
-      <c r="AD83">
-        <v>0</v>
+      <c r="AC83" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>34</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF83">
         <v>0</v>
@@ -12385,8 +13381,17 @@
       <c r="AJ83">
         <v>0</v>
       </c>
+      <c r="AK83">
+        <v>0</v>
+      </c>
+      <c r="AL83">
+        <v>0</v>
+      </c>
+      <c r="AM83">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="1:36">
+    <row r="84" spans="1:39">
       <c r="A84">
         <v>82</v>
       </c>
@@ -12471,14 +13476,14 @@
       <c r="AB84">
         <v>22</v>
       </c>
-      <c r="AC84">
-        <v>0</v>
-      </c>
-      <c r="AD84">
-        <v>0</v>
+      <c r="AC84" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>789</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF84">
         <v>0</v>
@@ -12495,8 +13500,17 @@
       <c r="AJ84">
         <v>0</v>
       </c>
+      <c r="AK84">
+        <v>0</v>
+      </c>
+      <c r="AL84">
+        <v>0</v>
+      </c>
+      <c r="AM84">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="1:36">
+    <row r="85" spans="1:39">
       <c r="A85">
         <v>83</v>
       </c>
@@ -12581,14 +13595,14 @@
       <c r="AB85">
         <v>22</v>
       </c>
-      <c r="AC85">
-        <v>0</v>
-      </c>
-      <c r="AD85">
-        <v>0</v>
+      <c r="AC85" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="AD85" t="s">
+        <v>34</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF85">
         <v>0</v>
@@ -12605,8 +13619,17 @@
       <c r="AJ85">
         <v>0</v>
       </c>
+      <c r="AK85">
+        <v>0</v>
+      </c>
+      <c r="AL85">
+        <v>0</v>
+      </c>
+      <c r="AM85">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="1:36">
+    <row r="86" spans="1:39">
       <c r="A86">
         <v>84</v>
       </c>
@@ -12691,14 +13714,14 @@
       <c r="AB86">
         <v>22</v>
       </c>
-      <c r="AC86">
-        <v>0</v>
-      </c>
-      <c r="AD86">
-        <v>0</v>
+      <c r="AC86" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>789</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF86">
         <v>0</v>
@@ -12715,8 +13738,17 @@
       <c r="AJ86">
         <v>0</v>
       </c>
+      <c r="AK86">
+        <v>0</v>
+      </c>
+      <c r="AL86">
+        <v>0</v>
+      </c>
+      <c r="AM86">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="1:36" ht="37.5">
+    <row r="87" spans="1:39">
       <c r="A87">
         <v>85</v>
       </c>
@@ -12801,14 +13833,14 @@
       <c r="AB87">
         <v>22</v>
       </c>
-      <c r="AC87">
-        <v>0</v>
-      </c>
-      <c r="AD87">
-        <v>0</v>
+      <c r="AC87" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>34</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF87">
         <v>0</v>
@@ -12825,8 +13857,17 @@
       <c r="AJ87">
         <v>0</v>
       </c>
+      <c r="AK87">
+        <v>0</v>
+      </c>
+      <c r="AL87">
+        <v>0</v>
+      </c>
+      <c r="AM87">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="1:36">
+    <row r="88" spans="1:39">
       <c r="A88">
         <v>86</v>
       </c>
@@ -12911,32 +13952,41 @@
       <c r="AB88">
         <v>22</v>
       </c>
-      <c r="AC88">
-        <v>0</v>
-      </c>
-      <c r="AD88">
+      <c r="AC88" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE88">
+        <v>22</v>
+      </c>
+      <c r="AF88">
+        <v>0</v>
+      </c>
+      <c r="AG88">
         <v>2</v>
       </c>
-      <c r="AE88">
-        <v>0</v>
-      </c>
-      <c r="AF88">
+      <c r="AH88">
+        <v>0</v>
+      </c>
+      <c r="AI88">
         <v>1</v>
       </c>
-      <c r="AG88">
-        <v>0</v>
-      </c>
-      <c r="AH88">
-        <v>0</v>
-      </c>
-      <c r="AI88">
-        <v>0</v>
-      </c>
       <c r="AJ88">
         <v>0</v>
       </c>
+      <c r="AK88">
+        <v>0</v>
+      </c>
+      <c r="AL88">
+        <v>0</v>
+      </c>
+      <c r="AM88">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="1:36">
+    <row r="89" spans="1:39">
       <c r="A89">
         <v>87</v>
       </c>
@@ -13021,14 +14071,14 @@
       <c r="AB89">
         <v>22</v>
       </c>
-      <c r="AC89">
-        <v>0</v>
-      </c>
-      <c r="AD89">
-        <v>0</v>
+      <c r="AC89" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>34</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -13045,8 +14095,17 @@
       <c r="AJ89">
         <v>0</v>
       </c>
+      <c r="AK89">
+        <v>0</v>
+      </c>
+      <c r="AL89">
+        <v>0</v>
+      </c>
+      <c r="AM89">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="1:36">
+    <row r="90" spans="1:39">
       <c r="A90">
         <v>88</v>
       </c>
@@ -13054,15 +14113,6 @@
       <c r="I90" s="5"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="AC90">
-        <v>0</v>
-      </c>
-      <c r="AD90">
-        <v>0</v>
-      </c>
-      <c r="AE90">
-        <v>0</v>
-      </c>
       <c r="AF90">
         <v>0</v>
       </c>
@@ -13078,8 +14128,17 @@
       <c r="AJ90">
         <v>0</v>
       </c>
+      <c r="AK90">
+        <v>0</v>
+      </c>
+      <c r="AL90">
+        <v>0</v>
+      </c>
+      <c r="AM90">
+        <v>0</v>
+      </c>
     </row>
-    <row r="91" spans="1:36">
+    <row r="91" spans="1:39">
       <c r="A91">
         <v>89</v>
       </c>
@@ -13088,7 +14147,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="1:36">
+    <row r="92" spans="1:39">
       <c r="A92">
         <v>90</v>
       </c>
@@ -13097,7 +14156,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="1:36">
+    <row r="93" spans="1:39">
       <c r="A93">
         <v>91</v>
       </c>
@@ -13106,7 +14165,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="1:36">
+    <row r="94" spans="1:39">
       <c r="A94">
         <v>92</v>
       </c>
@@ -13115,7 +14174,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="1:36">
+    <row r="95" spans="1:39">
       <c r="A95">
         <v>93</v>
       </c>
@@ -13124,7 +14183,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="1:36">
+    <row r="96" spans="1:39">
       <c r="A96">
         <v>94</v>
       </c>
